--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1351701.29</v>
+        <v>833728.29</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1232143.5</v>
+        <v>726111.79</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jonathan bush</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>926861</v>
+        <v>577821.36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>jonathan bush</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -555,11 +555,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
-        <v>858719.6899999999</v>
+        <v>538616</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>724500.6800000001</v>
+        <v>445549.88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>641479.13</v>
+        <v>374519.88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>490095</v>
+        <v>327070</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>392786.08</v>
+        <v>271405.58</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>332962</v>
+        <v>239331</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>289540.83</v>
+        <v>201197.62</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>269275</v>
+        <v>180548</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>27630.46</v>
+        <v>16677.67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5900</v>
+        <v>2800</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>946.0799999999999</v>
+        <v>550.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>23460</v>
+        <v>17705</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>675</v>
+        <v>575</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>720</v>
+        <v>420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>395</v>
+        <v>260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>833</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>974.49</v>
+        <v>640.26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>816.64</v>
+        <v>408.32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>950</v>
+        <v>475</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1001.22</v>
+        <v>751.22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4440,20 +4440,90 @@
         </is>
       </c>
       <c r="E3">
+        <v>500</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_106</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>trevor alex doiron</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>76</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
         <v>1000</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Representative_106</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_76</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4493,16 +4563,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trevor alex doiron</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>76</v>
+          <t>woodleigh h hughes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>78</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4510,20 +4580,90 @@
         </is>
       </c>
       <c r="E2">
+        <v>700</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_78</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>christopher alfred lewey</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>82</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
         <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Representative_76</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>Representative_82</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4563,37 +4703,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>woodleigh h hughes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>78</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>700</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_78</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>kimberly j pomerleau</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>85</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>790</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_85</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4633,37 +4773,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>christopher alfred lewey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>82</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_82</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>david wayne boyer jr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>87</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3483.7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_87</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4703,16 +4843,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kimberly j pomerleau</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>85</v>
+          <t>laurel libby</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>90</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4720,147 +4860,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1110</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_85</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>david wayne boyer jr</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>87</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>4408.7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_87</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>laurel libby</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>90</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>79297.60000000001</v>
+        <v>56333.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>7140</v>
+        <v>6065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>4751.73</v>
+        <v>2628.64</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3575</v>
+        <v>3325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5784,20 +5784,300 @@
         </is>
       </c>
       <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nathan burnett</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1789.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>matthea elisabeth larsen daughtry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>23</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_23</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>denise tepler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>225</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>april fournier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>114</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Senator_21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>Representative_114</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5837,7 +6117,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nathan burnett</t>
+          <t>teresa s pierce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5846,7 +6126,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5854,20 +6134,20 @@
         </is>
       </c>
       <c r="E2">
-        <v>1789.2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_22</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>2400</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5907,7 +6187,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matthea elisabeth larsen daughtry</t>
+          <t>peter g violette</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5916,286 +6196,6 @@
         </is>
       </c>
       <c r="C2">
-        <v>23</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_23</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>denise tepler</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>225</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_24</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>april fournier</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>114</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>200</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_114</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>teresa s pierce</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>25</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2400</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>peter g violette</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
         <v>26</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9645.309999999999</v>
+        <v>8295.309999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1420</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2257</v>
+        <v>1661</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3750</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2225</v>
+        <v>1725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1390</v>
+        <v>1290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>570</v>
+        <v>335</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -9,86 +9,107 @@
   <sheets>
     <sheet name="Governor" sheetId="1" r:id="rId1"/>
     <sheet name="Representative_1" sheetId="2" r:id="rId2"/>
-    <sheet name="Representative_13" sheetId="3" r:id="rId3"/>
-    <sheet name="Representative_14" sheetId="4" r:id="rId4"/>
-    <sheet name="Representative_16" sheetId="5" r:id="rId5"/>
-    <sheet name="Representative_17" sheetId="6" r:id="rId6"/>
-    <sheet name="Representative_18" sheetId="7" r:id="rId7"/>
-    <sheet name="Representative_23" sheetId="8" r:id="rId8"/>
-    <sheet name="Representative_24" sheetId="9" r:id="rId9"/>
-    <sheet name="Representative_25" sheetId="10" r:id="rId10"/>
-    <sheet name="Representative_27" sheetId="11" r:id="rId11"/>
-    <sheet name="Representative_30" sheetId="12" r:id="rId12"/>
-    <sheet name="Representative_31" sheetId="13" r:id="rId13"/>
-    <sheet name="Representative_32" sheetId="14" r:id="rId14"/>
-    <sheet name="Representative_33" sheetId="15" r:id="rId15"/>
-    <sheet name="Representative_38" sheetId="16" r:id="rId16"/>
-    <sheet name="Representative_39" sheetId="17" r:id="rId17"/>
-    <sheet name="Representative_41" sheetId="18" r:id="rId18"/>
-    <sheet name="Representative_43" sheetId="19" r:id="rId19"/>
-    <sheet name="Representative_45" sheetId="20" r:id="rId20"/>
-    <sheet name="Representative_48" sheetId="21" r:id="rId21"/>
-    <sheet name="Representative_58" sheetId="22" r:id="rId22"/>
-    <sheet name="Representative_59" sheetId="23" r:id="rId23"/>
-    <sheet name="Representative_61" sheetId="24" r:id="rId24"/>
-    <sheet name="Representative_63" sheetId="25" r:id="rId25"/>
-    <sheet name="Representative_64" sheetId="26" r:id="rId26"/>
-    <sheet name="Representative_71" sheetId="27" r:id="rId27"/>
-    <sheet name="Representative_72" sheetId="28" r:id="rId28"/>
-    <sheet name="Representative_75" sheetId="29" r:id="rId29"/>
-    <sheet name="Representative_76" sheetId="30" r:id="rId30"/>
-    <sheet name="Representative_78" sheetId="31" r:id="rId31"/>
-    <sheet name="Representative_82" sheetId="32" r:id="rId32"/>
-    <sheet name="Representative_85" sheetId="33" r:id="rId33"/>
-    <sheet name="Representative_87" sheetId="34" r:id="rId34"/>
-    <sheet name="Representative_90" sheetId="35" r:id="rId35"/>
-    <sheet name="Representative_94" sheetId="36" r:id="rId36"/>
-    <sheet name="Representative_96" sheetId="37" r:id="rId37"/>
-    <sheet name="Representative_98" sheetId="38" r:id="rId38"/>
-    <sheet name="Representative_100" sheetId="39" r:id="rId39"/>
-    <sheet name="Representative_101" sheetId="40" r:id="rId40"/>
-    <sheet name="Representative_106" sheetId="41" r:id="rId41"/>
-    <sheet name="Representative_112" sheetId="42" r:id="rId42"/>
-    <sheet name="Representative_114" sheetId="43" r:id="rId43"/>
-    <sheet name="Representative_117" sheetId="44" r:id="rId44"/>
-    <sheet name="Representative_119" sheetId="45" r:id="rId45"/>
-    <sheet name="Representative_120" sheetId="46" r:id="rId46"/>
-    <sheet name="Representative_122" sheetId="47" r:id="rId47"/>
-    <sheet name="Representative_123" sheetId="48" r:id="rId48"/>
-    <sheet name="Representative_129" sheetId="49" r:id="rId49"/>
-    <sheet name="Representative_132" sheetId="50" r:id="rId50"/>
-    <sheet name="Representative_133" sheetId="51" r:id="rId51"/>
-    <sheet name="Representative_134" sheetId="52" r:id="rId52"/>
-    <sheet name="Representative_137" sheetId="53" r:id="rId53"/>
-    <sheet name="Representative_139" sheetId="54" r:id="rId54"/>
-    <sheet name="Representative_143" sheetId="55" r:id="rId55"/>
-    <sheet name="Representative_145" sheetId="56" r:id="rId56"/>
-    <sheet name="Representative_149" sheetId="57" r:id="rId57"/>
-    <sheet name="Representative_150" sheetId="58" r:id="rId58"/>
-    <sheet name="Senator_2" sheetId="59" r:id="rId59"/>
-    <sheet name="Senator_3" sheetId="60" r:id="rId60"/>
-    <sheet name="Senator_4" sheetId="61" r:id="rId61"/>
-    <sheet name="Senator_5" sheetId="62" r:id="rId62"/>
-    <sheet name="Senator_7" sheetId="63" r:id="rId63"/>
-    <sheet name="Senator_8" sheetId="64" r:id="rId64"/>
-    <sheet name="Senator_9" sheetId="65" r:id="rId65"/>
-    <sheet name="Senator_11" sheetId="66" r:id="rId66"/>
-    <sheet name="Senator_12" sheetId="67" r:id="rId67"/>
-    <sheet name="Senator_15" sheetId="68" r:id="rId68"/>
-    <sheet name="Senator_16" sheetId="69" r:id="rId69"/>
-    <sheet name="Senator_17" sheetId="70" r:id="rId70"/>
-    <sheet name="Senator_18" sheetId="71" r:id="rId71"/>
-    <sheet name="Senator_21" sheetId="72" r:id="rId72"/>
-    <sheet name="Senator_22" sheetId="73" r:id="rId73"/>
-    <sheet name="Senator_23" sheetId="74" r:id="rId74"/>
-    <sheet name="Senator_24" sheetId="75" r:id="rId75"/>
-    <sheet name="Senator_25" sheetId="76" r:id="rId76"/>
-    <sheet name="Senator_26" sheetId="77" r:id="rId77"/>
-    <sheet name="Senator_29" sheetId="78" r:id="rId78"/>
-    <sheet name="Senator_32" sheetId="79" r:id="rId79"/>
-    <sheet name="Senator_33" sheetId="80" r:id="rId80"/>
-    <sheet name="Senator_34" sheetId="81" r:id="rId81"/>
-    <sheet name="Senator_35" sheetId="82" r:id="rId82"/>
+    <sheet name="Representative_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Representative_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Representative_10" sheetId="5" r:id="rId5"/>
+    <sheet name="Representative_13" sheetId="6" r:id="rId6"/>
+    <sheet name="Representative_14" sheetId="7" r:id="rId7"/>
+    <sheet name="Representative_16" sheetId="8" r:id="rId8"/>
+    <sheet name="Representative_17" sheetId="9" r:id="rId9"/>
+    <sheet name="Representative_18" sheetId="10" r:id="rId10"/>
+    <sheet name="Representative_21" sheetId="11" r:id="rId11"/>
+    <sheet name="Representative_23" sheetId="12" r:id="rId12"/>
+    <sheet name="Representative_24" sheetId="13" r:id="rId13"/>
+    <sheet name="Representative_25" sheetId="14" r:id="rId14"/>
+    <sheet name="Representative_26" sheetId="15" r:id="rId15"/>
+    <sheet name="Representative_27" sheetId="16" r:id="rId16"/>
+    <sheet name="Representative_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Representative_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Representative_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Representative_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Representative_38" sheetId="21" r:id="rId21"/>
+    <sheet name="Representative_39" sheetId="22" r:id="rId22"/>
+    <sheet name="Representative_41" sheetId="23" r:id="rId23"/>
+    <sheet name="Representative_43" sheetId="24" r:id="rId24"/>
+    <sheet name="Representative_45" sheetId="25" r:id="rId25"/>
+    <sheet name="Representative_48" sheetId="26" r:id="rId26"/>
+    <sheet name="Representative_52" sheetId="27" r:id="rId27"/>
+    <sheet name="Representative_55" sheetId="28" r:id="rId28"/>
+    <sheet name="Representative_56" sheetId="29" r:id="rId29"/>
+    <sheet name="Representative_58" sheetId="30" r:id="rId30"/>
+    <sheet name="Representative_59" sheetId="31" r:id="rId31"/>
+    <sheet name="Representative_61" sheetId="32" r:id="rId32"/>
+    <sheet name="Representative_63" sheetId="33" r:id="rId33"/>
+    <sheet name="Representative_64" sheetId="34" r:id="rId34"/>
+    <sheet name="Representative_71" sheetId="35" r:id="rId35"/>
+    <sheet name="Representative_72" sheetId="36" r:id="rId36"/>
+    <sheet name="Representative_75" sheetId="37" r:id="rId37"/>
+    <sheet name="Representative_76" sheetId="38" r:id="rId38"/>
+    <sheet name="Representative_78" sheetId="39" r:id="rId39"/>
+    <sheet name="Representative_82" sheetId="40" r:id="rId40"/>
+    <sheet name="Representative_85" sheetId="41" r:id="rId41"/>
+    <sheet name="Representative_87" sheetId="42" r:id="rId42"/>
+    <sheet name="Representative_88" sheetId="43" r:id="rId43"/>
+    <sheet name="Representative_90" sheetId="44" r:id="rId44"/>
+    <sheet name="Representative_94" sheetId="45" r:id="rId45"/>
+    <sheet name="Representative_95" sheetId="46" r:id="rId46"/>
+    <sheet name="Representative_96" sheetId="47" r:id="rId47"/>
+    <sheet name="Representative_98" sheetId="48" r:id="rId48"/>
+    <sheet name="Representative_100" sheetId="49" r:id="rId49"/>
+    <sheet name="Representative_101" sheetId="50" r:id="rId50"/>
+    <sheet name="Representative_103" sheetId="51" r:id="rId51"/>
+    <sheet name="Representative_106" sheetId="52" r:id="rId52"/>
+    <sheet name="Representative_108" sheetId="53" r:id="rId53"/>
+    <sheet name="Representative_112" sheetId="54" r:id="rId54"/>
+    <sheet name="Representative_114" sheetId="55" r:id="rId55"/>
+    <sheet name="Representative_115" sheetId="56" r:id="rId56"/>
+    <sheet name="Representative_117" sheetId="57" r:id="rId57"/>
+    <sheet name="Representative_119" sheetId="58" r:id="rId58"/>
+    <sheet name="Representative_120" sheetId="59" r:id="rId59"/>
+    <sheet name="Representative_121" sheetId="60" r:id="rId60"/>
+    <sheet name="Representative_122" sheetId="61" r:id="rId61"/>
+    <sheet name="Representative_123" sheetId="62" r:id="rId62"/>
+    <sheet name="Representative_129" sheetId="63" r:id="rId63"/>
+    <sheet name="Representative_132" sheetId="64" r:id="rId64"/>
+    <sheet name="Representative_133" sheetId="65" r:id="rId65"/>
+    <sheet name="Representative_134" sheetId="66" r:id="rId66"/>
+    <sheet name="Representative_135" sheetId="67" r:id="rId67"/>
+    <sheet name="Representative_137" sheetId="68" r:id="rId68"/>
+    <sheet name="Representative_138" sheetId="69" r:id="rId69"/>
+    <sheet name="Representative_139" sheetId="70" r:id="rId70"/>
+    <sheet name="Representative_143" sheetId="71" r:id="rId71"/>
+    <sheet name="Representative_145" sheetId="72" r:id="rId72"/>
+    <sheet name="Representative_149" sheetId="73" r:id="rId73"/>
+    <sheet name="Representative_150" sheetId="74" r:id="rId74"/>
+    <sheet name="Senator_1" sheetId="75" r:id="rId75"/>
+    <sheet name="Senator_2" sheetId="76" r:id="rId76"/>
+    <sheet name="Senator_3" sheetId="77" r:id="rId77"/>
+    <sheet name="Senator_4" sheetId="78" r:id="rId78"/>
+    <sheet name="Senator_5" sheetId="79" r:id="rId79"/>
+    <sheet name="Senator_7" sheetId="80" r:id="rId80"/>
+    <sheet name="Senator_8" sheetId="81" r:id="rId81"/>
+    <sheet name="Senator_9" sheetId="82" r:id="rId82"/>
+    <sheet name="Senator_10" sheetId="83" r:id="rId83"/>
+    <sheet name="Senator_11" sheetId="84" r:id="rId84"/>
+    <sheet name="Senator_12" sheetId="85" r:id="rId85"/>
+    <sheet name="Senator_15" sheetId="86" r:id="rId86"/>
+    <sheet name="Senator_16" sheetId="87" r:id="rId87"/>
+    <sheet name="Senator_17" sheetId="88" r:id="rId88"/>
+    <sheet name="Senator_18" sheetId="89" r:id="rId89"/>
+    <sheet name="Senator_20" sheetId="90" r:id="rId90"/>
+    <sheet name="Senator_21" sheetId="91" r:id="rId91"/>
+    <sheet name="Senator_22" sheetId="92" r:id="rId92"/>
+    <sheet name="Senator_23" sheetId="93" r:id="rId93"/>
+    <sheet name="Senator_24" sheetId="94" r:id="rId94"/>
+    <sheet name="Senator_25" sheetId="95" r:id="rId95"/>
+    <sheet name="Senator_26" sheetId="96" r:id="rId96"/>
+    <sheet name="Senator_29" sheetId="97" r:id="rId97"/>
+    <sheet name="Senator_30" sheetId="98" r:id="rId98"/>
+    <sheet name="Senator_31" sheetId="99" r:id="rId99"/>
+    <sheet name="Senator_32" sheetId="100" r:id="rId100"/>
+    <sheet name="Senator_33" sheetId="101" r:id="rId101"/>
+    <sheet name="Senator_34" sheetId="102" r:id="rId102"/>
+    <sheet name="Senator_35" sheetId="103" r:id="rId103"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +505,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>833728.29</v>
+        <v>1394419.29</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,7 +530,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>726111.79</v>
+        <v>1076389.11</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -520,7 +541,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>jonathan bush</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,11 +551,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>577821.36</v>
+        <v>964451</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,7 +566,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jonathan bush</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -555,11 +576,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
-        <v>538616</v>
+        <v>908323.62</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -584,7 +605,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>445549.88</v>
+        <v>643571.79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,7 +630,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>374519.88</v>
+        <v>566721.55</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -634,7 +655,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>327070</v>
+        <v>528575</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -659,7 +680,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>271405.58</v>
+        <v>510025.58</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -670,7 +691,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>owen mccarthy</t>
+          <t>david john jones</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -684,7 +705,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>239331</v>
+        <v>443208.33</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -695,7 +716,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>david john jones</t>
+          <t>owen mccarthy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -709,7 +730,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>201197.62</v>
+        <v>341972</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -734,7 +755,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>180548</v>
+        <v>254758</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -759,7 +780,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>16677.67</v>
+        <v>24426.82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -859,7 +880,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>264.7</v>
+        <v>364.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -937,16 +958,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jason shedlock</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>120</v>
+          <t>april fournier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -954,20 +975,20 @@
         </is>
       </c>
       <c r="E2">
-        <v>275</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_120</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>250</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_114</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1007,16 +1028,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matthew d beck</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>122</v>
+          <t>elizabeth caruso</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1440</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nicole c grohoski</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1024,69 +1115,69 @@
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_122</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>annie christy</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>123</v>
+        <v>1025</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>leo christopher kenney</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1094,157 +1185,745 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_123</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>marshall archer</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>129</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_129</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>john linnehan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>13</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Unenrolled</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2560</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_13</t>
+        <v>2980</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>michael tipping</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>joseph m baldacci</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>andrew zarro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>115</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_115</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>matthew moonen</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>117</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>750</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_117</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>michael dixon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>119</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>277</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_119</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>jason shedlock</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>450</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_120</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>robert cameron</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>121</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_121</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>matthew d beck</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>122</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_122</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>annie christy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>123</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1800</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_123</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>marshall archer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>129</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>150</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_129</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>john linnehan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2560</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>j mark worth</t>
         </is>
       </c>
@@ -1262,361 +1941,11 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Representative_13</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ryan m fecteau</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>132</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>125</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_132</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>marc g malon ii</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>133</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>275</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_133</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>allen anthony daggett</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>134</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Unenrolled</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>500</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_134</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>charles edward tilburg</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>137</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_137</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>jamie k newton</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>139</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>500</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_139</t>
         </is>
       </c>
     </row>
@@ -1763,6 +2092,496 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ryan m fecteau</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>132</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>125</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_132</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>marc g malon ii</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>133</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>275</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_133</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>allen anthony daggett</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>134</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_134</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rachel mary phipps</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>135</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_135</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>charles edward tilburg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>137</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_137</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>oliver mcavoy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>138</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_138</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>jamie k newton</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>139</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_139</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>gary friedmann</t>
         </is>
       </c>
@@ -1780,87 +2599,115 @@
         </is>
       </c>
       <c r="E2">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Representative_14</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>eric h small</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>143</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_143</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>jean donovan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>14</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>146</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eric h small</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>143</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_143</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>john robert henkelman iii</t>
         </is>
       </c>
@@ -1891,7 +2738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1961,7 +2808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2001,6 +2848,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>genevieve lemire</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>175</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>mallory aaren cook</t>
         </is>
       </c>
@@ -2018,7 +2935,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2031,7 +2948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2116,7 +3033,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2129,7 +3046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2227,7 +3144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2267,7 +3184,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>steven matthew bishop iv</t>
+          <t>steven matthew bishop</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2284,7 +3201,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4010</v>
+        <v>5570</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2297,7 +3214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2354,7 +3271,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>550.54</v>
+        <v>880.54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2367,7 +3284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2407,6 +3324,146 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>roland daniel martin</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>600</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>frank joseph casella</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>joschka winterling</t>
         </is>
       </c>
@@ -2424,87 +3481,115 @@
         </is>
       </c>
       <c r="E2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Representative_23</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>carolyn fish</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>17705</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>katie brydon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>23</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_23</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>carolyn fish</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>22540</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>sean f faircloth</t>
         </is>
       </c>
@@ -2522,7 +3607,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>575</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2558,12 +3643,40 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>zachary smith</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>16.66</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2603,6 +3716,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>laurie osher</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1370</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>daniel joseph ankeles</t>
         </is>
       </c>
@@ -2633,7 +3816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2673,16 +3856,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>laurie osher</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>25</v>
+          <t>james f dill</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>26</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2690,20 +3873,20 @@
         </is>
       </c>
       <c r="E2">
-        <v>420</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>950</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2829,7 +4012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2869,6 +4052,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>david h mccrea</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>950</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>james lee white</t>
         </is>
       </c>
@@ -2899,7 +4152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2984,7 +4237,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>260</v>
+        <v>465</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2997,7 +4250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3067,7 +4320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3137,7 +4390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3194,7 +4447,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>504</v>
+        <v>834</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3222,7 +4475,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3235,7 +4488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3305,9 +4558,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3362,88 +4615,186 @@
         </is>
       </c>
       <c r="E2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Representative_41</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>michael sweeny flanagan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>43</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>marcus mrowka</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>41</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_41</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>poppy t arford</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>101</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>408.32</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_101</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>chris p austin</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>43</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1186.8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>michael sweeny flanagan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3460,7 +4811,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>640.26</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3468,12 +4819,40 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rhiannon hampson</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>43</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>75</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_43</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3513,16 +4892,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>poppy t arford</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>101</v>
+          <t>rebecca stephens</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>45</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>475</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_45</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>charlotte nutt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>48</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3530,20 +4979,20 @@
         </is>
       </c>
       <c r="E2">
-        <v>408.32</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_101</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_48</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3583,16 +5032,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rebecca stephens</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>45</v>
+          <t>david wayne guilmette</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3600,20 +5049,20 @@
         </is>
       </c>
       <c r="E2">
-        <v>475</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_45</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>920</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_52</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3653,16 +5102,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>charlotte nutt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>48</v>
+          <t>maureen aucoin</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3670,20 +5119,90 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_48</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>1100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_55</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>robin uptonsukeforth</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>56</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>660</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_56</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3740,7 +5259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>975</v>
+        <v>1975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3809,7 +5328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3894,7 +5413,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>751.22</v>
+        <v>856.74</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3907,7 +5426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3964,7 +5483,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3977,7 +5496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4047,7 +5566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4087,6 +5606,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>karin orenstein</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1175</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_103</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>shawn michael packard</t>
         </is>
       </c>
@@ -4117,7 +5706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4174,7 +5763,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4187,7 +5776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4285,7 +5874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4355,7 +5944,427 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>trevor alex doiron</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>76</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_76</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>woodleigh h hughes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>78</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>700</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_78</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>christopher alfred lewey</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>82</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_82</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kimberly j pomerleau</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>85</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1390</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_85</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>david wayne boyer jr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>87</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>4308.7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_87</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dana staples</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>88</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>150</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_88</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4453,7 +6462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4493,16 +6502,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trevor alex doiron</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>76</v>
+          <t>laurel libby</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>90627.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_90</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>scott a harriman</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>94</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4510,427 +6589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_76</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>woodleigh h hughes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>78</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>700</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_78</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>christopher alfred lewey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>82</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_82</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>kimberly j pomerleau</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>85</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>790</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_85</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>david wayne boyer jr</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>87</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>3483.7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_87</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>laurel libby</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>90</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>56333.3</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_90</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>janet beaudoin</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>94</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>7316</v>
+        <v>33065.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4941,7 +6600,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kiernan innes majeruscollins</t>
+          <t>janet beaudoin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4954,11 +6613,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>6065</v>
+        <v>13041</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4969,7 +6628,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>scott a harriman</t>
+          <t>kiernan innes majeruscollins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4986,7 +6645,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>2628.64</v>
+        <v>7140</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4999,7 +6658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5039,7 +6698,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>luke jensen</t>
+          <t>kiernan majeruscollins</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>95</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>345</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_95</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kerryl lee clement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5052,512 +6781,736 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>10</v>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Representative_96</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>william j st michel</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>98</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>825</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_98</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ryan christopher otis</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sean mahoney</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>112</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>3325</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_112</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>nicole lynn kalloch</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>12</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Unenrolled</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1500</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_12</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>kati l mccormick</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>950</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_15</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>scott w cyrway</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>16</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>800</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_16</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>richard mason</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>17</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>250</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jeff timberlake</t>
+          <t>luke jensen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>96</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>35</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_96</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>william j st michel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>98</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_98</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lucien daigle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>105</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kevin oconnell</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>551</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ryan christopher otis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1300</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nicole lynn kalloch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ann higgins matlack</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kati l mccormick</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1050</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>kelly dearborn</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>108</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>10100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_108</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>scott w cyrway</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>800</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>patric moore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>richard mason</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>17</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>250</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jojean keller</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5570,13 +7523,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>jeff timberlake</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Republican</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>1.53</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_17</t>
         </is>
@@ -5587,7 +7568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5657,9 +7638,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5714,577 +7695,675 @@
         </is>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>820</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Senator_2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>shanna cox</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>21</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>nathan burnett</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1789.2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_22</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>matthea elisabeth larsen daughtry</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>23</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_23</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>denise tepler</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>225</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_24</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>april fournier</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>114</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_114</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>teresa s pierce</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>25</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2400</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>peter g violette</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>26</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2600</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_26</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>anne carney</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>29</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2005</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>harold hull</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eric brakey</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>800</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>shanna cox</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>205</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nathan burnett</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1789.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>matthea elisabeth larsen daughtry</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>23</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_23</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>denise tepler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1025</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>teresa s pierce</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2400</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sean mahoney</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>112</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3325</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_112</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>peter g violette</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>26</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>anne carney</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>29</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2805</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>vincent maietta</t>
         </is>
       </c>
@@ -6315,7 +8394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6372,7 +8451,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8295.309999999999</v>
+        <v>8965.52</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6385,47 +8464,47 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>henry l ingwersen</t>
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sophia warren</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6434,7 +8513,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6442,18 +8521,186 @@
         </is>
       </c>
       <c r="E2">
-        <v>2250</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_32</t>
+        <v>3435</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>john murphy salamone</t>
+          <t>eleanor sato</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>3000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>donna bailey</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>henry l ingwersen</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>32</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2950</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jason g litalien</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6466,11 +8713,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>1110</v>
+        <v>1400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6481,7 +8728,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jason g litalien</t>
+          <t>john murphy salamone</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6494,11 +8741,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>1100</v>
+        <v>1315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6511,7 +8758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6596,7 +8843,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6609,7 +8856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6694,7 +8941,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1661</v>
+        <v>2356</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6707,7 +8954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6764,7 +9011,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6792,7 +9039,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1725</v>
+        <v>3186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6805,7 +9052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6890,7 +9137,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1290</v>
+        <v>1657</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6957,424 +9204,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>elizabeth caruso</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>335</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_5</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>matthew moonen</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>117</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>750</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_117</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>nicole c grohoski</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1025</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_7</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>leo christopher kenney</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>2980</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_8</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>joseph m baldacci</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_9</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>michael dixon</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>119</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>52</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Representative_119</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>858719.6899999999</v>
+        <v>858719.6900000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>724500.6800000001</v>
+        <v>724500.6800000028</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>816.64</v>
+        <v>816.6399999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -4778,7 +4778,7 @@
 
 <file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4838,82 +4838,110 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Senator_7</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>party</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_con_per_cand</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>michael tipping</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>3050</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senator_8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>cheryl hewes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>35.71</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_con_per_cand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>michael tipping</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3050</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Senator_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>leo christopher kenney</t>
         </is>
       </c>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2845</v>
+        <v>2855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -4165,7 +4165,7 @@
 
 <file path=xl/worksheets/sheet118.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4203,7 +4203,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>amanda noelle collamore</t>
+          <t>zachary lejonhud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4214,13 +4214,8 @@
       <c r="C2">
         <v>68</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
       <c r="E2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4231,7 +4226,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brian j blake</t>
+          <t>amanda noelle collamore</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4244,13 +4239,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_68</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>brian j blake</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>68</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_68</t>
         </is>
@@ -6428,7 +6451,7 @@
 
 <file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6522,7 +6545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>caldwell jackson</t>
+          <t>azalea cormier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6533,13 +6556,8 @@
       <c r="C4">
         <v>80</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6550,7 +6568,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>roberta j hill</t>
+          <t>caldwell jackson</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6563,13 +6581,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>roberta j hill</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_80</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>33315.76</v>
+        <v>250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>janet beaudoin</t>
+          <t>kendil elizabeth snowblack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>13041</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kendil elizabeth snowblack</t>
+          <t>kristen sarah cloutier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
@@ -8887,7 +8887,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kristen sarah cloutier</t>
+          <t>janet beaudoin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -1125,7 +1125,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>angus s iii king</t>
+          <t>angus king iii</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>michael perkins</t>
+          <t>michael d perkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9167,7 +9167,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>joseph edwards velozo</t>
+          <t>luke jensen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9178,13 +9178,8 @@
       <c r="C4">
         <v>96</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
       <c r="E4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9195,7 +9190,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>david c projansky</t>
+          <t>joseph edwards velozo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9208,7 +9203,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
@@ -9223,7 +9218,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>luke dylan jensen</t>
+          <t>david c projansky</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9233,6 +9228,11 @@
       </c>
       <c r="C6">
         <v>96</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
       </c>
       <c r="E6">
         <v>0</v>
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2855</v>
+        <v>2850</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>michael cunningham ii</t>
+          <t>michael hobart cunningham ii</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20001,7 +20001,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rebecca flood andrews</t>
+          <t>rebecca lynn flood andrews</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23533,7 +23533,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>anthony weaver</t>
+          <t>anthony m weaver</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -26649,7 +26649,7 @@
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -26827,7 +26827,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>christopher austin</t>
+          <t>ann h matlack</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -26840,41 +26840,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>Representative_43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ann h matlack</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>43</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>Representative_43</t>
         </is>
@@ -27587,7 +27559,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>james william iii hunt</t>
+          <t>erik hobson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -27604,7 +27576,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -27615,7 +27587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>holly beth stover</t>
+          <t>james william iii hunt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -27628,7 +27600,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -27643,7 +27615,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>erik hobson</t>
+          <t>holly beth stover</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -27656,7 +27628,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -900,7 +900,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>derek allen levasseur</t>
+          <t>w edward crockett</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>1190</v>
+        <v>12067.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>steven christopher sheppard</t>
+          <t>kenneth a capron</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>1100</v>
+        <v>3505</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>alexander kenneth murchison</t>
+          <t>derek allen levasseur</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>880.04</v>
+        <v>1190</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kenneth forrest pinet</t>
+          <t>steven christopher sheppard</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,11 +985,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E18">
-        <v>645</v>
+        <v>1100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>james libby</t>
+          <t>alexander kenneth murchison</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E19">
-        <v>364.7</v>
+        <v>880.04</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>kenneth forrest pinet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E20">
-        <v>180</v>
+        <v>645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>john michael sr glowa</t>
+          <t>james libby</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1060,11 +1060,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>364.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>maria michela aguilo</t>
+          <t>john michael glowa sr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1085,11 +1085,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jason seth cherry</t>
+          <t>john michael sr glowa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E23">
@@ -1125,7 +1125,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>angus king iii</t>
+          <t>maria michela aguilo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E24">
@@ -1167,6 +1167,31 @@
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>andrew parker</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Governor</t>
         </is>
@@ -2327,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2421,7 +2446,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dexter buzz bridges</t>
+          <t>jeff harris</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2432,8 +2457,13 @@
       <c r="C4">
         <v>58</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E4">
-        <v>755</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2444,7 +2474,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nicholas alexander</t>
+          <t>dexter buzz bridges</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2461,7 +2491,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>147.7</v>
+        <v>755</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2472,7 +2502,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lawrence e jr bessey</t>
+          <t>nicholas alexander</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2489,7 +2519,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>147.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2500,7 +2530,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sharon conrad frost</t>
+          <t>lawrence e jr bessey</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2513,7 +2543,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E7">
@@ -2528,7 +2558,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>daniel jesse newman</t>
+          <t>sharon conrad frost</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2541,7 +2571,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E8">
@@ -2556,7 +2586,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dexter bridges jr</t>
+          <t>daniel jesse newman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2576,6 +2606,34 @@
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>Representative_58</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dexter bridges jr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Representative_58</t>
         </is>
@@ -2588,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2626,7 +2684,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>john reny</t>
+          <t>tom keefe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2639,11 +2697,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>1250</v>
+        <v>2545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2654,7 +2712,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>marcus emerson</t>
+          <t>john reny</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2671,7 +2729,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>856.74</v>
+        <v>1250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2682,7 +2740,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>katrina couch raysaulis</t>
+          <t>marcus emerson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2695,11 +2753,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>856.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2710,7 +2768,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>david m rollins</t>
+          <t>katrina couch raysaulis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2738,7 +2796,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>thomas keefe</t>
+          <t>david m rollins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2758,6 +2816,34 @@
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>Representative_59</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thomas keefe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>59</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Representative_59</t>
         </is>
@@ -3890,7 +3976,7 @@
 
 <file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3939,6 +4025,11 @@
       <c r="C2">
         <v>66</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E2">
         <v>0</v>
       </c>
@@ -3979,7 +4070,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>michael d perkins</t>
+          <t>alicia barnes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3992,41 +4083,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>Representative_66</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>alicia barnes</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>66</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_66</t>
         </is>
@@ -4214,6 +4277,11 @@
       <c r="C2">
         <v>68</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E2">
         <v>50</v>
       </c>
@@ -4538,7 +4606,7 @@
 
 <file path=xl/worksheets/sheet120.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4576,7 +4644,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jantzen stephen craine</t>
+          <t>matthew rush</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4589,11 +4657,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>406.15</v>
+        <v>1820</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4604,7 +4672,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corinne s sternlieb</t>
+          <t>jantzen stephen craine</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4617,11 +4685,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>406.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4632,7 +4700,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gregory l swallow</t>
+          <t>corinne s sternlieb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4645,13 +4713,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gregory l swallow</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_7</t>
         </is>
@@ -5070,7 +5166,7 @@
 
 <file path=xl/worksheets/sheet124.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5108,7 +5204,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ryan morgan</t>
+          <t>mike soboleski</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5125,7 +5221,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>1375</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5136,7 +5232,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>michael arthur soboleski</t>
+          <t>ryan morgan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5153,7 +5249,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5164,7 +5260,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vincent m house</t>
+          <t>michael arthur soboleski</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5177,7 +5273,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -5192,7 +5288,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kevin lee scott</t>
+          <t>vincent m house</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5205,7 +5301,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
@@ -5220,7 +5316,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>daniel simonds</t>
+          <t>kevin lee scott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5233,7 +5329,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E6">
@@ -5248,7 +5344,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tiffany bond</t>
+          <t>daniel simonds</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5261,13 +5357,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Representative_73</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tiffany bond</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>73</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Unenrolled</t>
         </is>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Representative_73</t>
         </is>
@@ -5280,7 +5404,7 @@
 
 <file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5422,29 +5546,6 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>Representative_74</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>marc edwards</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>74</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_74</t>
         </is>
@@ -5457,7 +5558,7 @@
 
 <file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5523,7 +5624,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>h scott jr landry</t>
+          <t>h scott landry</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5540,7 +5641,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5551,7 +5652,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stephan m bunker</t>
+          <t>h scott jr landry</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5571,6 +5672,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_75</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>stephan m bunker</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_75</t>
         </is>
@@ -5583,7 +5712,7 @@
 
 <file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5677,7 +5806,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sheila a lyman</t>
+          <t>clinton brooks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5690,7 +5819,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
@@ -5705,7 +5834,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tamara n hoke</t>
+          <t>sheila a lyman</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5718,13 +5847,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_76</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tamara n hoke</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>76</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_76</t>
         </is>
@@ -6556,6 +6713,11 @@
       <c r="C4">
         <v>80</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E4">
         <v>10</v>
       </c>
@@ -7188,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7226,7 +7388,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kimberly j pomerleau</t>
+          <t>timothy nickels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7243,7 +7405,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2680</v>
+        <v>1025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7254,7 +7416,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy nickels</t>
+          <t>adrienne paul</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7271,7 +7433,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7282,7 +7444,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>adrienne paul</t>
+          <t>travis b erickson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7295,11 +7457,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7310,7 +7472,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>travis b erickson</t>
+          <t>paul welch</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7330,34 +7492,6 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>Representative_85</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>paul welch</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>85</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_85</t>
         </is>
@@ -7370,7 +7504,7 @@
 
 <file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7408,7 +7542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rolf arthur jr olsen</t>
+          <t>rolf arthur olsen jr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7425,7 +7559,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7436,7 +7570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>craig r messinger</t>
+          <t>rolf arthur jr olsen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7449,7 +7583,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -7464,7 +7598,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gregory e foster</t>
+          <t>craig r messinger</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7477,7 +7611,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
@@ -7492,7 +7626,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>abigail geer</t>
+          <t>gregory e foster</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7505,13 +7639,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_86</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>abigail geer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>86</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_86</t>
         </is>
@@ -7657,6 +7819,11 @@
       <c r="C5">
         <v>87</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -8541,7 +8708,7 @@
 
 <file path=xl/worksheets/sheet145.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8607,7 +8774,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stephen j wood</t>
+          <t>scott girardin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8620,13 +8787,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_92</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stephen j wood</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>92</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_92</t>
         </is>
@@ -8765,7 +8960,7 @@
 
 <file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8803,7 +8998,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scott a harriman</t>
+          <t>kiernan innes majeruscollins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8820,7 +9015,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>8521.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8831,7 +9026,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kendil elizabeth snowblack</t>
+          <t>scott a harriman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8844,11 +9039,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8859,7 +9054,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kristen sarah cloutier</t>
+          <t>kendil elizabeth snowblack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8872,7 +9067,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -8887,7 +9082,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>janet beaudoin</t>
+          <t>kristen sarah cloutier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8900,13 +9095,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_94</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>janet beaudoin</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>94</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_94</t>
         </is>
@@ -9073,7 +9296,7 @@
 
 <file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9167,7 +9390,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>luke jensen</t>
+          <t>joseph edwards velozo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9178,8 +9401,13 @@
       <c r="C4">
         <v>96</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9190,7 +9418,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>joseph edwards velozo</t>
+          <t>david c projansky</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9203,7 +9431,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
@@ -9218,7 +9446,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>david c projansky</t>
+          <t>michel a lajoie</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9238,34 +9466,6 @@
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>Representative_96</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>michel a lajoie</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>96</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>Representative_96</t>
         </is>
@@ -9278,7 +9478,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9344,7 +9544,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scott w jordan</t>
+          <t>jason lewis copp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9372,7 +9572,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jason copp</t>
+          <t>scott w jordan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9392,6 +9592,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_110</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>jason copp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_110</t>
         </is>
@@ -11056,7 +11284,7 @@
 
 <file path=xl/worksheets/sheet161.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11094,7 +11322,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>richard mason</t>
+          <t>richard g mason</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11111,7 +11339,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>2225.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11122,7 +11350,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jojean keller</t>
+          <t>richard mason</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11135,11 +11363,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11150,7 +11378,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jeff timberlake</t>
+          <t>jojean keller</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11163,11 +11391,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>1.53</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -11178,7 +11406,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>thomas riley watson</t>
+          <t>jeff timberlake</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11191,11 +11419,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -11206,7 +11434,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>joshua morris</t>
+          <t>thomas riley watson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11219,13 +11447,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>Senator_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>joshua morris</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Senator_17</t>
         </is>
@@ -11602,7 +11858,7 @@
 
 <file path=xl/worksheets/sheet164.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11640,7 +11896,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matthew rush</t>
+          <t>harold hull</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11657,7 +11913,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1820</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11668,7 +11924,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>harold hull</t>
+          <t>harold trey l iii stewart</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11681,41 +11937,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>Senator_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>harold trey l iii stewart</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Senator</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_2</t>
         </is>
@@ -12071,6 +12299,11 @@
       <c r="C6">
         <v>21</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -12087,7 +12320,7 @@
 
 <file path=xl/worksheets/sheet167.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -12125,7 +12358,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nathan burnett</t>
+          <t>kimberly j pomerleau</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12138,11 +12371,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1789.2</v>
+        <v>2680</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12153,7 +12386,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kimberly pomerleau</t>
+          <t>nathan burnett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12166,11 +12399,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1789.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12181,7 +12414,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>anne marie mcmahon</t>
+          <t>kimberly pomerleau</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12194,13 +12427,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Senator_22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>anne marie mcmahon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Senator_22</t>
         </is>
@@ -14901,7 +15162,7 @@
 
 <file path=xl/worksheets/sheet184.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14939,7 +15200,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>billy faulkingham</t>
+          <t>billy bob faulkingham</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14956,7 +15217,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10010</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15043,6 +15304,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Senator_6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aaron dana</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Senator_6</t>
         </is>
@@ -15279,7 +15568,7 @@
 
 <file path=xl/worksheets/sheet187.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -15421,6 +15710,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Senator_9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stephen carey</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Senator_9</t>
         </is>
@@ -15433,7 +15750,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -15499,7 +15816,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jacob murray wakem</t>
+          <t>dylan pugh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15512,41 +15829,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>Representative_114</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dylan pugh</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>114</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_114</t>
         </is>
@@ -15653,7 +15942,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lucien jb daigle</t>
+          <t>dana marie appleby</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -15666,7 +15955,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
@@ -16199,7 +16488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>charles a skold</t>
+          <t>jacob murray wakem</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16212,7 +16501,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -16227,7 +16516,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jacob wakem</t>
+          <t>charles a skold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16240,7 +16529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
@@ -16259,7 +16548,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -16297,7 +16586,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>billy bob faulkingham</t>
+          <t>thomas hart</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16314,7 +16603,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10010</v>
+        <v>300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16325,7 +16614,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>norman edward bamford</t>
+          <t>edward mathias kamin iii</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16338,7 +16627,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
@@ -16353,7 +16642,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>thomas hart jr</t>
+          <t>norman edward bamford</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16366,13 +16655,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thomas hart jr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_12</t>
         </is>
@@ -17260,6 +17577,11 @@
       <c r="C2">
         <v>124</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E2">
         <v>1000</v>
       </c>
@@ -17906,7 +18228,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -18039,6 +18361,11 @@
       <c r="C5">
         <v>13</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -18051,7 +18378,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>michael hobart cunningham ii</t>
+          <t>russell patrick white</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18064,7 +18391,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E6">
@@ -18079,7 +18406,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>russell patrick white</t>
+          <t>cheryl ann hewes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18099,34 +18426,6 @@
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>Representative_13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cheryl ann hewes</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>Representative_13</t>
         </is>
@@ -18265,7 +18564,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -18379,6 +18678,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_131</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kenneth blow</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_131</t>
         </is>
@@ -18867,7 +19194,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -19009,6 +19336,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_135</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>scott craig</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>135</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_135</t>
         </is>
@@ -19861,7 +20216,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -19938,6 +20293,11 @@
       <c r="C3">
         <v>141</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E3">
         <v>1000</v>
       </c>
@@ -19961,6 +20321,11 @@
       <c r="C4">
         <v>141</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
       <c r="E4">
         <v>0</v>
       </c>
@@ -20001,7 +20366,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rebecca lynn flood andrews</t>
+          <t>clinton phinney jr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20014,7 +20379,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E6">
@@ -20029,7 +20394,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>clinton phinney jr</t>
+          <t>lucas john lanigan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20057,7 +20422,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lucas john lanigan</t>
+          <t>patricia e kidder</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20070,41 +20435,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>Representative_141</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>patricia e kidder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>141</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Democratic</t>
-        </is>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>Representative_141</t>
         </is>
@@ -20628,6 +20965,11 @@
       <c r="C2">
         <v>144</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E2">
         <v>50</v>
       </c>
@@ -21232,7 +21574,7 @@
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -21374,6 +21716,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_149</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>justin tahai</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>149</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_149</t>
         </is>
@@ -21386,7 +21756,7 @@
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -21452,7 +21822,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jason m joyce</t>
+          <t>clifford noyes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -21472,6 +21842,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>jason m joyce</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_15</t>
         </is>
@@ -21610,7 +22008,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -21676,7 +22074,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>melanie fleming sachs</t>
+          <t>henry lawrence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -21689,11 +22087,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -21704,7 +22102,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>henry lawrence iii</t>
+          <t>melanie fleming sachs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -21717,7 +22115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
@@ -21732,7 +22130,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>james j jr finegan</t>
+          <t>henry lawrence iii</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21752,6 +22150,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_102</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>james j jr finegan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>102</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_102</t>
         </is>
@@ -21913,7 +22339,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E2">
@@ -23444,7 +23870,7 @@
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -23521,6 +23947,11 @@
       <c r="C3">
         <v>25</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E3">
         <v>0</v>
       </c>
@@ -23533,7 +23964,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>anthony m weaver</t>
+          <t>thomas casey</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -23553,34 +23984,6 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>Representative_25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>thomas casey</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Representative</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Republican</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_25</t>
         </is>
@@ -23593,7 +23996,7 @@
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -23687,7 +24090,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zachary t wyles</t>
+          <t>edward l paradis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -23715,7 +24118,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>edward paradis</t>
+          <t>zachary t wyles</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -23735,6 +24138,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>edward paradis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_26</t>
         </is>
@@ -24076,6 +24507,11 @@
       <c r="C2">
         <v>29</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
       <c r="E2">
         <v>1000</v>
       </c>
@@ -24386,7 +24822,7 @@
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -24452,7 +24888,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>w louis jr sidell</t>
+          <t>john j contreni jr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -24480,7 +24916,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>john contreni jr</t>
+          <t>w louis jr sidell</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -24500,6 +24936,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>john contreni jr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_30</t>
         </is>
@@ -25485,6 +25949,11 @@
       <c r="C5">
         <v>36</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -26859,7 +27328,7 @@
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -26897,7 +27366,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brady alden clark</t>
+          <t>ray thombs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -26914,7 +27383,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1570.65</v>
+        <v>3069.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26925,7 +27394,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ray alden jr thombs</t>
+          <t>brady alden clark</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -26942,7 +27411,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1570.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26953,7 +27422,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>william d pluecker</t>
+          <t>ray alden jr thombs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -26966,7 +27435,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -26981,7 +27450,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>shawn saindon</t>
+          <t>william d pluecker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -26992,10 +27461,43 @@
       <c r="C5">
         <v>44</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>shawn saindon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>44</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_44</t>
         </is>
@@ -27393,6 +27895,11 @@
       <c r="C2">
         <v>47</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E2">
         <v>1000</v>
       </c>
@@ -27878,6 +28385,11 @@
       <c r="C2">
         <v>5</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
       <c r="E2">
         <v>1000</v>
       </c>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -16930,7 +16930,7 @@
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -17016,6 +17016,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>jack mccarthy</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_3</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jason cherry</t>
+          <t>john michael glowa sr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,11 +985,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E18">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>andrew parker</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,34 +1014,9 @@
         </is>
       </c>
       <c r="E19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>andrew parker</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Unenrolled</t>
-        </is>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>Governor</t>
         </is>
@@ -15502,7 +15477,7 @@
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -15560,6 +15535,34 @@
         <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jonathan goble</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>18</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>880.54</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Representative_18</t>
         </is>
@@ -17910,7 +17913,7 @@
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -17948,7 +17951,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>benjamin charles hymes</t>
+          <t>jason cherry</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17961,11 +17964,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17976,7 +17979,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kayla miller</t>
+          <t>benjamin charles hymes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17989,13 +17992,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>kayla miller</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>38</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_38</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -16779,7 +16779,7 @@
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -16845,7 +16845,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>james michael michaud</t>
+          <t>nancy theriaultspecial</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16873,7 +16873,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nancy jean theriault</t>
+          <t>james michael michaud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16901,7 +16901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nancy mcdowell</t>
+          <t>nancy jean theriault</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16914,13 +16914,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>Representative_29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nancy mcdowell</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>29</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Representative_29</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>james libby</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,11 +985,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E18">
-        <v>180</v>
+        <v>364.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1000,23 +1000,48 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>john michael glowa sr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>andrew parker</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Governor</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Unenrolled</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Governor</t>
         </is>
@@ -1127,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1213,6 +1238,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_51</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>louis larios</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>51</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_51</t>
         </is>
@@ -1841,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1955,6 +2008,34 @@
         <v>755</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_58</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lawrence e bessey jr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>58</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_58</t>
         </is>
@@ -4207,7 +4288,7 @@
 
 <file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4293,6 +4374,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_77</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nicole bambrick</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>77</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_77</t>
         </is>
@@ -6419,7 +6528,7 @@
 
 <file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6485,7 +6594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matthew kershaw</t>
+          <t>bret michael martel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6498,13 +6607,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_95</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>matthew kershaw</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>95</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_95</t>
         </is>
@@ -8799,7 +8936,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8857,6 +8994,34 @@
         <v>3325</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_112</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lauren chelsea jones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Representative_112</t>
         </is>
@@ -9849,7 +10014,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9907,6 +10072,34 @@
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_113</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lisa nelthropp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>113</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Representative_113</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -18200,7 +18200,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>benjamin charles hymes</t>
+          <t>kayla miller</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18213,11 +18213,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kayla miller</t>
+          <t>benjamin charles hymes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18241,7 +18241,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -14112,7 +14112,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rebecca lynn flood andrews</t>
+          <t>clinton phinney jr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14125,11 +14125,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>clinton phinney jr</t>
+          <t>rebecca lynn flood andrews</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>andrew laverdiere</t>
+          <t>ambureen rana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -16156,7 +16156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ambureen rana</t>
+          <t>andrew laverdiere</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16169,11 +16169,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1370</v>
+        <v>1456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1907115.63</v>
+        <v>2054400.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1584663.72</v>
+        <v>1737457.03</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1294195</v>
+        <v>1417470</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>nirav shah</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1126648.2</v>
+        <v>1215075.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nirav shah</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1016244.87</v>
+        <v>1195462.47</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>847237.2</v>
+        <v>938356.86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>810890.88</v>
+        <v>860406.88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>617415.98</v>
+        <v>659587.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>489932.78</v>
+        <v>500207.78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>379099</v>
+        <v>385349</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>295748</v>
+        <v>330923</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>161581.33</v>
+        <v>176533.38</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>35804.54</v>
+        <v>40306.84</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>karen l montell</t>
+          <t>michelle tucker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1525,11 +1525,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1825</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>michelle tucker</t>
+          <t>karen l montell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -1610,7 +1610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>maureen aucoin</t>
+          <t>charles hippler iv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>charles hippler iv</t>
+          <t>maureen aucoin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>660</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6910.91</v>
+        <v>7619.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2545</v>
+        <v>2860</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pamela jo swift</t>
+          <t>katrina j smith</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2617,11 +2617,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>819</v>
+        <v>1550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>katrina j smith</t>
+          <t>pamela jo swift</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2645,11 +2645,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>819</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5650</v>
+        <v>7550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1885</v>
+        <v>2235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matthew channing townsend</t>
+          <t>shawn m dixon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3107,11 +3107,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shawn m dixon</t>
+          <t>matthew channing townsend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3135,11 +3135,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>856</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1820</v>
+        <v>1870</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>406.15</v>
+        <v>966.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5025</v>
+        <v>6685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1375</v>
+        <v>3225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ryan morgan</t>
+          <t>daniel simonds</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3919,11 +3919,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>daniel simonds</t>
+          <t>ryan morgan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11055</v>
+        <v>13255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2050</v>
+        <v>2150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tammy l schmersalburgess</t>
+          <t>arlie hetrick jr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4339,11 +4339,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>arlie hetrick jr</t>
+          <t>tammy l schmersalburgess</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -4452,7 +4452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>woodleigh h hughes</t>
+          <t>rachel a henderson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4465,11 +4465,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rachel a henderson</t>
+          <t>woodleigh h hughes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4437.6</v>
+        <v>5512.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>665</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cassandra anne dove</t>
+          <t>mark walker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5249,11 +5249,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mark walker</t>
+          <t>cassandra anne dove</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5277,11 +5277,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1025</v>
+        <v>1683.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1440</v>
+        <v>1736.89</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dana staples</t>
+          <t>quentin chapman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1150</v>
+        <v>3591.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quentin chapman</t>
+          <t>dana staples</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5795,11 +5795,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13036.25</v>
+        <v>13236.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8521.02</v>
+        <v>8672.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bret michael martel</t>
+          <t>matthew kershaw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>264.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>matthew kershaw</t>
+          <t>bret michael martel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>christina rue cork mitchell</t>
+          <t>jason lewis copp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6803,11 +6803,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jason lewis copp</t>
+          <t>christina rue cork mitchell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>craig v hickman</t>
+          <t>steven mcgee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7713,11 +7713,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>steven mcgee</t>
+          <t>craig v hickman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12275</v>
+        <v>15355</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4025</v>
+        <v>4650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3325</v>
+        <v>3575</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>anne carney</t>
+          <t>vincent maietta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9421,11 +9421,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>2805</v>
+        <v>17000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vincent maietta</t>
+          <t>anne carney</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9449,11 +9449,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>7830</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10732.51</v>
+        <v>10932.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4040</v>
+        <v>5490</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>4559.3</v>
+        <v>5039</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>3050</v>
+        <v>4050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10010</v>
+        <v>11860</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kenneth davis jr</t>
+          <t>aaron dana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10695,11 +10695,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aaron dana</t>
+          <t>kenneth davis jr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16974</v>
+        <v>25643.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>3315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>33417</v>
+        <v>37216</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3250</v>
+        <v>4250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2970</v>
+        <v>3120</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1225</v>
+        <v>2275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1300</v>
+        <v>2305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3600</v>
+        <v>4600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>520</v>
+        <v>4145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gordon frohloff</t>
+          <t>ayn hanselmann</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14321,11 +14321,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ayn hanselmann</t>
+          <t>gordon frohloff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -15011,7 +15011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>maura h pillsbury</t>
+          <t>henry lawrence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -15301,11 +15301,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>henry lawrence</t>
+          <t>maura h pillsbury</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>710</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>880.54</v>
+        <v>915.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1456</v>
+        <v>1691</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>david h mccrea</t>
+          <t>susan bernard</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17205,11 +17205,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>950</v>
+        <v>2950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>susan bernard</t>
+          <t>david h mccrea</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17233,11 +17233,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8631.76</v>
+        <v>11781.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>2850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4081.8</v>
+        <v>5156.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1640</v>
+        <v>2470</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3069.8</v>
+        <v>4419.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>563.84</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13415</v>
+        <v>15215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2054400.95</v>
+        <v>2054609.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1215075.3</v>
+        <v>1215210.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>938356.86</v>
+        <v>941931.86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>860406.88</v>
+        <v>860506.88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1683.65</v>
+        <v>1883.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11860</v>
+        <v>11865</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2054609.95</v>
+        <v>2190265.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1737457.03</v>
+        <v>1877877.51</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1417470</v>
+        <v>1520770</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1215210.3</v>
+        <v>1406661.85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1195462.47</v>
+        <v>1261086.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>941931.86</v>
+        <v>1030864.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>860506.88</v>
+        <v>906579.88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>659587.97</v>
+        <v>699659.96</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>500207.78</v>
+        <v>510482.78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>385349</v>
+        <v>389224</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>330923</v>
+        <v>359773</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>176533.38</v>
+        <v>191285.43</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>40306.84</v>
+        <v>44809.14</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1825</v>
+        <v>3650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2400</v>
+        <v>3750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7619.56</v>
+        <v>8328.210000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2860</v>
+        <v>3130</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1550</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7550</v>
+        <v>9450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2235</v>
+        <v>2585</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1256</v>
+        <v>1656</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>606</v>
+        <v>1162</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1870</v>
+        <v>1920</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>966.15</v>
+        <v>1526.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6685</v>
+        <v>8345</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3225</v>
+        <v>5075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>305</v>
+        <v>610</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13255</v>
+        <v>14355</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5512.6</v>
+        <v>5887.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>380</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gino valeriani</t>
+          <t>azalea cormier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>830</v>
+        <v>1315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>azalea cormier</t>
+          <t>gino valeriani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4885,11 +4885,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>665</v>
+        <v>830</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1883.65</v>
+        <v>2283.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1736.89</v>
+        <v>2033.78</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3591.7</v>
+        <v>6383.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13236.25</v>
+        <v>13436.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8672.02</v>
+        <v>8723.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>264.01</v>
+        <v>528.02</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>275</v>
+        <v>450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peter j southam</t>
+          <t>joseph edward martin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8301,11 +8301,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>2835</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joseph edward martin</t>
+          <t>peter j southam</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8329,11 +8329,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>2100</v>
+        <v>2835</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15355</v>
+        <v>17885</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>495</v>
+        <v>695</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4650</v>
+        <v>5150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3575</v>
+        <v>3825</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>17000</v>
+        <v>33000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>7830</v>
+        <v>12855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10932.51</v>
+        <v>11132.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5490</v>
+        <v>6590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5039</v>
+        <v>5518.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>4050</v>
+        <v>5050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11865</v>
+        <v>13170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>720</v>
+        <v>1440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>446</v>
+        <v>642</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>25643.8</v>
+        <v>34063.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3315</v>
+        <v>4900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>37216</v>
+        <v>40165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4250</v>
+        <v>5250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3120</v>
+        <v>3270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2275</v>
+        <v>3325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2305</v>
+        <v>3310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4600</v>
+        <v>5600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4145</v>
+        <v>7620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mallory aaren cook</t>
+          <t>timothy towne</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14979,11 +14979,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy towne</t>
+          <t>mallory aaren cook</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1350</v>
+        <v>1990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>915.54</v>
+        <v>950.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1691</v>
+        <v>2012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2950</v>
+        <v>5900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11781.76</v>
+        <v>14931.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5156.8</v>
+        <v>5681.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2470</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4419.8</v>
+        <v>5769.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>563.84</v>
+        <v>1127.68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15215</v>
+        <v>16565</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>1030864.12</v>
+        <v>1031864.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>1031864.12</v>
+        <v>1035139.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2190265.3</v>
+        <v>1892270.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1877877.51</v>
+        <v>1673857.13</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1520770</v>
+        <v>1406495</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nirav shah</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1406661.85</v>
+        <v>1171439.47</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>nirav shah</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1261086.74</v>
+        <v>1149771.54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>troy dale jackson</t>
+          <t>robert b charles</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E7">
-        <v>1035139.12</v>
+        <v>841282.88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>robert b charles</t>
+          <t>troy dale jackson</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,11 +735,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E8">
-        <v>906579.88</v>
+        <v>828772.21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>699659.96</v>
+        <v>626612.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>510482.78</v>
+        <v>456282.78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>389224</v>
+        <v>362524</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>359773</v>
+        <v>224521</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>191285.43</v>
+        <v>160788.38</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>44809.14</v>
+        <v>40266.84</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>1390</v>
+        <v>1290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3650</v>
+        <v>1800</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3750</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1360</v>
+        <v>1310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8328.210000000001</v>
+        <v>7619.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3130</v>
+        <v>2860</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>1050</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9450</v>
+        <v>6550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2585</v>
+        <v>2230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1656</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1162</v>
+        <v>606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1920</v>
+        <v>1870</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1526.15</v>
+        <v>966.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8345</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5075</v>
+        <v>3225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14355</v>
+        <v>12255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2250</v>
+        <v>2150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>1100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5887.6</v>
+        <v>5512.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>760</v>
+        <v>380</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>azalea cormier</t>
+          <t>gino valeriani</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1315</v>
+        <v>830</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gino valeriani</t>
+          <t>azalea cormier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4885,11 +4885,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
-        <v>830</v>
+        <v>665</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1300</v>
+        <v>650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2283.65</v>
+        <v>1883.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2033.78</v>
+        <v>1736.89</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6383.4</v>
+        <v>2591.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13436.25</v>
+        <v>11226.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>90627.3</v>
+        <v>80627.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8723.02</v>
+        <v>7172.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>528.02</v>
+        <v>264.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1490</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>450</v>
+        <v>275</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2225.5</v>
+        <v>1225.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9104.48</v>
+        <v>7604.48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2965</v>
+        <v>2915</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>joseph edward martin</t>
+          <t>peter j southam</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8301,11 +8301,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>3100</v>
+        <v>2835</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peter j southam</t>
+          <t>joseph edward martin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8329,11 +8329,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>2835</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>17885</v>
+        <v>15355</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3108</v>
+        <v>2988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>695</v>
+        <v>395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5150</v>
+        <v>4650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3825</v>
+        <v>3575</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1840</v>
+        <v>1740</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>33000</v>
+        <v>17000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>12855</v>
+        <v>7830</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11132.51</v>
+        <v>10932.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6590</v>
+        <v>4490</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>daniel sayre</t>
+          <t>jonathan reed fallon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>3055</v>
+        <v>3044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jonathan reed fallon</t>
+          <t>daniel sayre</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10191,11 +10191,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>3044</v>
+        <v>2930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6225</v>
+        <v>5725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5518.7</v>
+        <v>4539</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>5050</v>
+        <v>4050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13170</v>
+        <v>11865</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1440</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>642</v>
+        <v>446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>34063.6</v>
+        <v>16643.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4900</v>
+        <v>3315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>40165</v>
+        <v>28216</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5250</v>
+        <v>3250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3270</v>
+        <v>3120</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3325</v>
+        <v>1775</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3310</v>
+        <v>2305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5600</v>
+        <v>4600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7620</v>
+        <v>3145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>timothy towne</t>
+          <t>mallory aaren cook</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14979,11 +14979,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mallory aaren cook</t>
+          <t>timothy towne</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15007,11 +15007,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950.54</v>
+        <v>915.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2012</v>
+        <v>1691</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5900</v>
+        <v>2950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14931.76</v>
+        <v>11781.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5681.8</v>
+        <v>5156.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3100</v>
+        <v>2470</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5769.8</v>
+        <v>3919.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1570.65</v>
+        <v>1370.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1127.68</v>
+        <v>563.84</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16565</v>
+        <v>14715</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>4093.18</v>
+        <v>3455.68</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1892270.95</v>
+        <v>2190265.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1673857.13</v>
+        <v>1877877.51</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1406495</v>
+        <v>1520770</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>nirav shah</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1171439.47</v>
+        <v>1406661.85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nirav shah</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1149771.54</v>
+        <v>1261086.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>robert b charles</t>
+          <t>troy dale jackson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E7">
-        <v>841282.88</v>
+        <v>1035139.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>troy dale jackson</t>
+          <t>robert b charles</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,11 +735,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E8">
-        <v>828772.21</v>
+        <v>906579.88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>626612.97</v>
+        <v>699659.96</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>456282.78</v>
+        <v>510482.78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>362524</v>
+        <v>389224</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>224521</v>
+        <v>359773</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>160788.38</v>
+        <v>191285.43</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>40266.84</v>
+        <v>44809.14</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1800</v>
+        <v>3650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2400</v>
+        <v>3750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1310</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7619.56</v>
+        <v>8328.210000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2860</v>
+        <v>3130</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6550</v>
+        <v>9450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2230</v>
+        <v>2585</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1256</v>
+        <v>1656</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>606</v>
+        <v>1162</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1870</v>
+        <v>1920</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>966.15</v>
+        <v>1526.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5685</v>
+        <v>8345</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3225</v>
+        <v>5075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>305</v>
+        <v>610</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12255</v>
+        <v>14355</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5512.6</v>
+        <v>5887.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>380</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gino valeriani</t>
+          <t>azalea cormier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>830</v>
+        <v>1315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>azalea cormier</t>
+          <t>gino valeriani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4885,11 +4885,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>665</v>
+        <v>830</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1883.65</v>
+        <v>2283.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1736.89</v>
+        <v>2033.78</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2591.7</v>
+        <v>6383.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11226.25</v>
+        <v>13436.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>80627.3</v>
+        <v>90627.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7172.02</v>
+        <v>8723.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>264.01</v>
+        <v>528.02</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1390</v>
+        <v>1490</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>275</v>
+        <v>450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1225.5</v>
+        <v>2225.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7604.48</v>
+        <v>9104.48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2915</v>
+        <v>2965</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peter j southam</t>
+          <t>joseph edward martin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8301,11 +8301,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>2835</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joseph edward martin</t>
+          <t>peter j southam</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8329,11 +8329,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1100</v>
+        <v>2835</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15355</v>
+        <v>17885</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2988</v>
+        <v>3108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>395</v>
+        <v>695</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4650</v>
+        <v>5150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3575</v>
+        <v>3825</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1740</v>
+        <v>1840</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>17000</v>
+        <v>33000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>7830</v>
+        <v>12855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10932.51</v>
+        <v>11132.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4490</v>
+        <v>6590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jonathan reed fallon</t>
+          <t>daniel sayre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10163,11 +10163,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>3044</v>
+        <v>3055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>daniel sayre</t>
+          <t>jonathan reed fallon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10191,11 +10191,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>2930</v>
+        <v>3044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5725</v>
+        <v>6225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>4539</v>
+        <v>5518.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>4050</v>
+        <v>5050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11865</v>
+        <v>13170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>720</v>
+        <v>1440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>446</v>
+        <v>642</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16643.8</v>
+        <v>34063.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3315</v>
+        <v>4900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>28216</v>
+        <v>40165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3120</v>
+        <v>3270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1775</v>
+        <v>3325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2305</v>
+        <v>3310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4600</v>
+        <v>5600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3145</v>
+        <v>7620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mallory aaren cook</t>
+          <t>timothy towne</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14979,11 +14979,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy towne</t>
+          <t>mallory aaren cook</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15007,11 +15007,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1350</v>
+        <v>1990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>915.54</v>
+        <v>950.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1691</v>
+        <v>2012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2950</v>
+        <v>5900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11781.76</v>
+        <v>14931.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1250</v>
+        <v>2250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5156.8</v>
+        <v>5681.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2470</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3919.8</v>
+        <v>5769.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1370.65</v>
+        <v>1570.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>563.84</v>
+        <v>1127.68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14715</v>
+        <v>16565</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3455.68</v>
+        <v>4093.18</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1490</v>
+        <v>1300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -17038,7 +17038,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nancy theriaultspecial</t>
+          <t>nancy mcdowell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17051,11 +17051,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>james michael michaud</t>
+          <t>nancy theriaultspecial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nancy jean theriault</t>
+          <t>james michael michaud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17122,7 +17122,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nancy mcdowell</t>
+          <t>nancy jean theriault</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E6">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -17066,7 +17066,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nancy theriaultspecial</t>
+          <t>nancy jean theriault</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>james michael michaud</t>
+          <t>nancy theriaultspecial</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17122,7 +17122,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nancy jean theriault</t>
+          <t>james michael michaud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2190265.3</v>
+        <v>2050515.93</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1877877.51</v>
+        <v>1663628.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1520770</v>
+        <v>1447420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1406661.85</v>
+        <v>1244866.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1261086.74</v>
+        <v>1193608.86</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>1035139.12</v>
+        <v>907375.0699999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>906579.88</v>
+        <v>725903.62</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>699659.96</v>
+        <v>656791.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>510482.78</v>
+        <v>499329.22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>389224</v>
+        <v>386123</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>359773</v>
+        <v>337068</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>191285.43</v>
+        <v>175753.68</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>44809.14</v>
+        <v>43598.19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>12067.98</v>
+        <v>8835</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>3505</v>
+        <v>3450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>1390</v>
+        <v>1150</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>james libby</t>
+          <t>john michael glowa sr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,11 +985,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E18">
-        <v>364.7</v>
+        <v>1150</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>james libby</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E19">
-        <v>180</v>
+        <v>364.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rafael leo macias</t>
+          <t>annalyse sarvinas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>annalyse sarvinas</t>
+          <t>rafael leo macias</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>920</v>
+        <v>820</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3650</v>
+        <v>2565</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3750</v>
+        <v>2700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1360</v>
+        <v>1660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8328.210000000001</v>
+        <v>7619.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3130</v>
+        <v>3222.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>400</v>
+        <v>980</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mark c cooper</t>
+          <t>joseph campbell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2323,11 +2323,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>690</v>
+        <v>1145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joseph campbell</t>
+          <t>mark c cooper</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2351,11 +2351,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>4500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9450</v>
+        <v>7550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2585</v>
+        <v>3930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1656</v>
+        <v>1170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1162</v>
+        <v>1006</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1920</v>
+        <v>2020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1526.15</v>
+        <v>981.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8345</v>
+        <v>6685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5075</v>
+        <v>3925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>610</v>
+        <v>380</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14355</v>
+        <v>13970</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2250</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5887.6</v>
+        <v>5925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>760</v>
+        <v>880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1315</v>
+        <v>1020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>830</v>
+        <v>750</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>marygrace caroline cimino</t>
+          <t>timothy becker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5151,11 +5151,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy becker</t>
+          <t>marygrace caroline cimino</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1300</v>
+        <v>650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2283.65</v>
+        <v>2072.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>adrienne paul</t>
+          <t>paul welch</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5375,11 +5375,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>paul welch</t>
+          <t>adrienne paul</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2033.78</v>
+        <v>1896.89</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tiffany strout</t>
+          <t>keith newman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>keith newman</t>
+          <t>tiffany strout</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6383.4</v>
+        <v>3091.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1150</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13436.25</v>
+        <v>12760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>90627.3</v>
+        <v>73158.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>james sorcek</t>
+          <t>pamela hart</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6089,11 +6089,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>305</v>
+        <v>700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pamela hart</t>
+          <t>james sorcek</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6117,11 +6117,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8723.02</v>
+        <v>8201</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>528.02</v>
+        <v>927.53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cheryl a golek</t>
+          <t>braeden webber</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7125,11 +7125,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>braeden webber</t>
+          <t>cheryl a golek</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7153,11 +7153,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>262</v>
+        <v>700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3030</v>
+        <v>3105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>450</v>
+        <v>2905</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>1350</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9104.48</v>
+        <v>9604.48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bruce bickford</t>
+          <t>michael r scott</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8497,11 +8497,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>3000</v>
+        <v>2935</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>michael r scott</t>
+          <t>bruce bickford</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8525,11 +8525,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>3000</v>
+        <v>2885</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>17885</v>
+        <v>18280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3108</v>
+        <v>2463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kimberly j pomerleau</t>
+          <t>nathan burnett</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8721,11 +8721,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>2680</v>
+        <v>2994.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nathan burnett</t>
+          <t>kimberly j pomerleau</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8749,11 +8749,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1789.2</v>
+        <v>2680</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1190</v>
+        <v>1050</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5150</v>
+        <v>4425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3825</v>
+        <v>3575</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2850</v>
+        <v>2975</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1840</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>33000</v>
+        <v>17000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>12855</v>
+        <v>8330</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11132.51</v>
+        <v>11406.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3435</v>
+        <v>3425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2950</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1405</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6590</v>
+        <v>5925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>3005</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6002</v>
+        <v>6076</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3186</v>
+        <v>3101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6225</v>
+        <v>6120</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5518.7</v>
+        <v>5974.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>5050</v>
+        <v>2250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1657</v>
+        <v>1540</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1440</v>
+        <v>1335</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13170</v>
+        <v>12790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>925</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>michael tipping</t>
+          <t>leo christopher kenney</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10891,11 +10891,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>3050</v>
+        <v>2980</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leo christopher kenney</t>
+          <t>michael tipping</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10919,11 +10919,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>2980</v>
+        <v>2400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1440</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>642</v>
+        <v>1031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>34063.6</v>
+        <v>26685.78</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4900</v>
+        <v>3640</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>277</v>
+        <v>1482</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>40165</v>
+        <v>38336</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>1050</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>genevieve lemire</t>
+          <t>william r tuell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12123,11 +12123,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>william r tuell</t>
+          <t>genevieve lemire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12151,11 +12151,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mary shannon lindstrom</t>
+          <t>eric nathanson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12221,11 +12221,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1060</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eric nathanson</t>
+          <t>mary shannon lindstrom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12249,11 +12249,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5250</v>
+        <v>4325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lynn holland copeland</t>
+          <t>todd michael davis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12823,11 +12823,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>todd michael davis</t>
+          <t>lynn holland copeland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -12908,7 +12908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>robert kelly</t>
+          <t>kenneth blow</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12921,11 +12921,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kenneth blow</t>
+          <t>robert kelly</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12949,11 +12949,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3270</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3626</v>
+        <v>3600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3325</v>
+        <v>2275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>1035</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3310</v>
+        <v>2555</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5600</v>
+        <v>5100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7620</v>
+        <v>5925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1867.72</v>
+        <v>1672.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>clinton phinney jr</t>
+          <t>rebecca lynn flood andrews</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14125,11 +14125,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rebecca lynn flood andrews</t>
+          <t>clinton phinney jr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14153,11 +14153,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>1160</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>995</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>timothy towne</t>
+          <t>mallory aaren cook</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14979,11 +14979,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mallory aaren cook</t>
+          <t>timothy towne</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1990</v>
+        <v>1450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950.54</v>
+        <v>1095.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frank joseph casella</t>
+          <t>ambureen rana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
@@ -16128,7 +16128,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ambureen rana</t>
+          <t>frank joseph casella</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16141,11 +16141,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>325</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>katie brydon</t>
+          <t>brian ames</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
@@ -16352,7 +16352,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brian ames</t>
+          <t>katie brydon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16365,11 +16365,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>victoria porter kornfield</t>
+          <t>joschka winterling</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>725</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>joschka winterling</t>
+          <t>victoria porter kornfield</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>395</v>
+        <v>700</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1175</v>
+        <v>975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2012</v>
+        <v>2555</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>820</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nancy mcdowellspecial</t>
+          <t>nancy mcdowell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nancy mcdowell</t>
+          <t>nancy mcdowellspecial</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17055,7 +17055,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5900</v>
+        <v>3050</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1350</v>
+        <v>500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1350</v>
+        <v>500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14931.76</v>
+        <v>11506.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>42.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jason cherry</t>
+          <t>kayla miller</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18189,7 +18189,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>310</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kayla miller</t>
+          <t>jason cherry</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joshua d gerritsen</t>
+          <t>marcus mrowka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>marcus mrowka</t>
+          <t>joshua d gerritsen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5681.8</v>
+        <v>4779.74</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3100</v>
+        <v>2575</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5769.8</v>
+        <v>4769.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brady alden clark</t>
+          <t>shawn saindon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19081,11 +19081,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>1570.65</v>
+        <v>1013.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shawn saindon</t>
+          <t>brady alden clark</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19109,11 +19109,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>1127.68</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16565</v>
+        <v>16740</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>4093.18</v>
+        <v>2705.18</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kristine a poland</t>
+          <t>jennifer mayher</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19277,7 +19277,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
@@ -19292,7 +19292,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jennifer mayher</t>
+          <t>kristine a poland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19305,11 +19305,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>chester b grover iii</t>
+          <t>wayne k farrin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
@@ -19390,7 +19390,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wayne k farrin</t>
+          <t>chester b grover iii</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19403,11 +19403,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>43598.19</v>
+        <v>44598.19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -900,7 +900,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>w edward crockett</t>
+          <t>james libby</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -910,11 +910,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E15">
-        <v>8835</v>
+        <v>15259.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kenneth a capron</t>
+          <t>w edward crockett</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -935,11 +935,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E16">
-        <v>3450</v>
+        <v>8835</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>derek allen levasseur</t>
+          <t>kenneth a capron</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -960,11 +960,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E17">
-        <v>1150</v>
+        <v>3450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>derek allen levasseur</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>james libby</t>
+          <t>john michael glowa sr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E19">
-        <v>364.7</v>
+        <v>1150</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>david wayne guilmette</t>
+          <t>sally jeane cluchey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1329,11 +1329,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sally jeane cluchey</t>
+          <t>david wayne guilmette</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1357,11 +1357,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>richard marc goldman</t>
+          <t>michael h lemelin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>michael h lemelin</t>
+          <t>richard marc goldman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>robin crawley</t>
+          <t>alicia c collins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>202</v>
+        <v>9175.120000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alicia c collins</t>
+          <t>robin crawley</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trevor alex doiron</t>
+          <t>sheila a lyman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
@@ -4228,7 +4228,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>clinton brooks</t>
+          <t>trevor alex doiron</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sheila a lyman</t>
+          <t>clinton brooks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1200</v>
+        <v>1201.53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scott a harriman</t>
+          <t>janet beaudoin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6481,11 +6481,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>janet beaudoin</t>
+          <t>scott a harriman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6509,11 +6509,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jason lewis copp</t>
+          <t>christina rue cork mitchell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
@@ -6818,7 +6818,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>christina rue cork mitchell</t>
+          <t>jason lewis copp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6831,11 +6831,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vaughn j mclaughlin</t>
+          <t>lucien daigle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7223,11 +7223,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1634</v>
+        <v>2555</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lucien daigle</t>
+          <t>vaughn j mclaughlin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7251,11 +7251,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>155</v>
+        <v>1634</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>steven mcgee</t>
+          <t>craig v hickman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7713,11 +7713,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>3500</v>
+        <v>4400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>craig v hickman</t>
+          <t>steven mcgee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7741,11 +7741,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peter g violette</t>
+          <t>kenneth james cianchette</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3000</v>
+        <v>9450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy e nangle</t>
+          <t>peter g violette</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9183,11 +9183,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>2975</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kenneth james cianchette</t>
+          <t>timothy e nangle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2975</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aaron dana</t>
+          <t>kenneth davis jr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10695,11 +10695,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>925</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kenneth davis jr</t>
+          <t>aaron dana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10723,11 +10723,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>todd michael davis</t>
+          <t>lynn holland copeland</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12823,11 +12823,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lynn holland copeland</t>
+          <t>todd michael davis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12851,11 +12851,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>275</v>
+        <v>1275</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>michelle kathryn conners</t>
+          <t>john michael eder</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>john michael eder</t>
+          <t>michelle kathryn conners</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -14700,7 +14700,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>walter gerard jr runte</t>
+          <t>bradley s moulton</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14713,11 +14713,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bradley s moulton</t>
+          <t>walter gerard jr runte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13010</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2250</v>
+        <v>3500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>alan lee orcutt</t>
+          <t>reagan leeann paul</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18087,11 +18087,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>950</v>
+        <v>15250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>reagan leeann paul</t>
+          <t>alan lee orcutt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18115,11 +18115,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d michael ray</t>
+          <t>joseph milton mclaughlin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18479,11 +18479,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>joseph milton mclaughlin</t>
+          <t>d michael ray</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18507,11 +18507,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -7466,7 +7466,7 @@
 
 <file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7552,6 +7552,34 @@
         <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>roy gott</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_12</t>
         </is>
@@ -8250,7 +8278,7 @@
 
 <file path=xl/worksheets/sheet163.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8336,6 +8364,34 @@
         <v>2835</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>david duguay</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_19</t>
         </is>
@@ -12534,7 +12590,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -12592,6 +12648,34 @@
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_128</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lawrence mcwilliams</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>128</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Representative_128</t>
         </is>
@@ -13136,7 +13220,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -13194,6 +13278,34 @@
         <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Representative_133</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>marc lessard</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>133</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Representative_133</t>
         </is>
@@ -14419,7 +14531,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E2">
@@ -14830,7 +14942,7 @@
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14916,6 +15028,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_148</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>noah cobb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>148</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_148</t>
         </is>
@@ -16678,7 +16818,7 @@
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -16764,6 +16904,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adam shaw</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>26</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_26</t>
         </is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1250</v>
+        <v>1370</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2072.9</v>
+        <v>2213.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1896.89</v>
+        <v>2721.89</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1672.72</v>
+        <v>2472.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>760</v>
+        <v>792.27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>andrew r torbett</t>
+          <t>eric boothroyd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17597,11 +17597,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eric boothroyd</t>
+          <t>andrew r torbett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17625,11 +17625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4769.8</v>
+        <v>8019.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2050515.93</v>
+        <v>2432116.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1663628.1</v>
+        <v>1672883.28</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1244866.65</v>
+        <v>1246868.85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1193608.86</v>
+        <v>1194028.86</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>907375.0699999999</v>
+        <v>912130.76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>725903.62</v>
+        <v>778029.76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>656791.97</v>
+        <v>688181.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>386123</v>
+        <v>386477.21</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>337068</v>
+        <v>337118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>44598.19</v>
+        <v>44638.19</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2020</v>
+        <v>2070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3925</v>
+        <v>4425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13970</v>
+        <v>15070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5925</v>
+        <v>6025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>timothy becker</t>
+          <t>marygrace caroline cimino</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5151,11 +5151,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>marygrace caroline cimino</t>
+          <t>timothy becker</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5179,11 +5179,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2721.89</v>
+        <v>2821.89</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6183.7</v>
+        <v>6783.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>3850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>christina rue cork mitchell</t>
+          <t>jason lewis copp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6803,11 +6803,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jason lewis copp</t>
+          <t>christina rue cork mitchell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -7728,7 +7728,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>craig v hickman</t>
+          <t>steven mcgee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7741,11 +7741,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>4400</v>
+        <v>5000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>steven mcgee</t>
+          <t>craig v hickman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7769,11 +7769,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>3500</v>
+        <v>4733.34</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>18280</v>
+        <v>19730</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4425</v>
+        <v>5775</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3575</v>
+        <v>4075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9450</v>
+        <v>12000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11406.51</v>
+        <v>12406.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5925</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3005</v>
+        <v>3015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6076</v>
+        <v>6198.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12790</v>
+        <v>16440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3640</v>
+        <v>3715</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1482</v>
+        <v>1532</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>38336</v>
+        <v>39041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3100</v>
+        <v>4835</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2500</v>
+        <v>2850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2275</v>
+        <v>2775</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>408.32</v>
+        <v>658.3199999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mallory aaren cook</t>
+          <t>timothy towne</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -15119,11 +15119,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>timothy towne</t>
+          <t>mallory aaren cook</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -15893,7 +15893,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1095.54</v>
+        <v>1115.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>roland daniel martin</t>
+          <t>roger clarence albert</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16057,11 +16057,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>roger clarence albert</t>
+          <t>roland daniel martin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16085,11 +16085,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3050</v>
+        <v>4550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>510</v>
+        <v>625</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11506.76</v>
+        <v>11526.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2575</v>
+        <v>2625</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8019.8</v>
+        <v>8319.799999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16740</v>
+        <v>18040</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2705.18</v>
+        <v>3756.18</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>778029.76</v>
+        <v>792720.92</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>337118</v>
+        <v>337168</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>8330</v>
+        <v>10405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5925</v>
+        <v>6775</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3500</v>
+        <v>3630.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15250</v>
+        <v>15275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2625</v>
+        <v>2870</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2432116.4</v>
+        <v>3039523.78</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nirav shah</t>
+          <t>robert b charles</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -660,11 +660,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E5">
-        <v>1246868.85</v>
+        <v>1334066.66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>nirav shah</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1194028.86</v>
+        <v>1246868.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>troy dale jackson</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>912130.76</v>
+        <v>1194028.86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>robert b charles</t>
+          <t>troy dale jackson</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,11 +735,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E8">
-        <v>792720.92</v>
+        <v>912130.76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>688181.97</v>
+        <v>781017.95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hannah pingree</t>
+          <t>jonathan bush</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -585,11 +585,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>3039523.78</v>
+        <v>3217769.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shenna bellows</t>
+          <t>hannah pingree</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1672883.28</v>
+        <v>3041723.78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jonathan bush</t>
+          <t>angus s king iii</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -635,11 +635,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>1447420</v>
+        <v>2065629.93</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>robert b charles</t>
+          <t>shenna bellows</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -660,11 +660,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
-        <v>1334066.66</v>
+        <v>1914913.56</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1246868.85</v>
+        <v>1478574.28</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>angus s king iii</t>
+          <t>robert b charles</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -710,11 +710,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E7">
-        <v>1194028.86</v>
+        <v>1335066.66</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>troy dale jackson</t>
+          <t>benjamin midgley</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,11 +735,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E8">
-        <v>912130.76</v>
+        <v>1136899</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>richard bennett</t>
+          <t>troy dale jackson</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -760,11 +760,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E9">
-        <v>781017.95</v>
+        <v>1079415.73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>david john jones</t>
+          <t>richard bennett</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -785,11 +785,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E10">
-        <v>499329.22</v>
+        <v>781022.95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>owen mccarthy</t>
+          <t>david john jones</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>386477.21</v>
+        <v>553696.87</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>benjamin midgley</t>
+          <t>owen mccarthy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>337168</v>
+        <v>541291.22</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>175753.68</v>
+        <v>232302.82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>44638.19</v>
+        <v>63962.58</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>james libby</t>
+          <t>john michael glowa sr</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -910,11 +910,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E15">
-        <v>15259.7</v>
+        <v>29583.92</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w edward crockett</t>
+          <t>derek allen levasseur</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>8835</v>
+        <v>24847.78</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kenneth a capron</t>
+          <t>james libby</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>3450</v>
+        <v>17389.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>derek allen levasseur</t>
+          <t>w edward crockett</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>1150</v>
+        <v>9317.98</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>john michael glowa sr</t>
+          <t>kenneth a capron</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E19">
-        <v>1150</v>
+        <v>3316.87</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>990</v>
+        <v>993.59</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1000.66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>3228.75</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2565</v>
+        <v>4805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3300</v>
+        <v>9833.75</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1386.18</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7619.56</v>
+        <v>12371.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3222.5</v>
+        <v>8222.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>melanie ann tompkins</t>
+          <t>donald james ardell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>146.23</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>donald james ardell</t>
+          <t>melanie ann tompkins</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9175.120000000001</v>
+        <v>13301.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4700</v>
+        <v>8733.43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>7550</v>
+        <v>14367.43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>945</v>
+        <v>945.03</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3930</v>
+        <v>4050.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>523</v>
+        <v>423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
 
 <file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scott strom</t>
+          <t>jeremy r mcarthur</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2946,6 +2946,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_65</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scott strom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>65</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_65</t>
         </is>
@@ -3111,7 +3139,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1170</v>
+        <v>5106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3139,7 +3167,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1000.08</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3192,7 +3220,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zachary lejonhud</t>
+          <t>amanda noelle collamore</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3205,11 +3233,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1006</v>
+        <v>5022.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3220,7 +3248,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>amanda noelle collamore</t>
+          <t>zachary lejonhud</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3233,11 +3261,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3307,7 +3335,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>650</v>
+        <v>2410.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3335,7 +3363,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>2198.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3405,7 +3433,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>10100</v>
+        <v>11200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3433,7 +3461,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3486,7 +3514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matthew rush</t>
+          <t>jantzen stephen craine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3499,11 +3527,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>2070</v>
+        <v>4408.48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3514,7 +3542,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jantzen stephen craine</t>
+          <t>matthew rush</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3527,11 +3555,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>981.15</v>
+        <v>2070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3601,7 +3629,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1500</v>
+        <v>3134.46</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3727,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6685</v>
+        <v>8141.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3825,7 +3853,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>900</v>
+        <v>919.47</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3895,7 +3923,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4425</v>
+        <v>5475</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4004,7 +4032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>russell john black</t>
+          <t>marc edwards</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4017,11 +4045,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1480</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4032,7 +4060,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>marc edwards</t>
+          <t>russell john black</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4045,11 +4073,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4119,7 +4147,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15070</v>
+        <v>26355.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4147,7 +4175,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2000</v>
+        <v>7900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4343,7 +4371,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>115</v>
+        <v>580</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4469,7 +4497,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2350</v>
+        <v>3574.58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4497,7 +4525,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4567,7 +4595,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6025</v>
+        <v>9136.700000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4595,7 +4623,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4665,7 +4693,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4693,7 +4721,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>170</v>
+        <v>1120</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4763,7 +4791,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1200</v>
+        <v>2450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4833,7 +4861,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2200</v>
+        <v>4720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4844,7 +4872,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>azalea cormier</t>
+          <t>gino valeriani</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4857,11 +4885,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1020</v>
+        <v>1995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4872,7 +4900,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gino valeriani</t>
+          <t>azalea cormier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4885,11 +4913,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
-        <v>750</v>
+        <v>1020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4942,7 +4970,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>christopher easton</t>
+          <t>peter conley wood</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4955,11 +4983,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>4551.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4970,7 +4998,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peter conley wood</t>
+          <t>christopher easton</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4983,11 +5011,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5057,7 +5085,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5085,7 +5113,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5155,7 +5183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2080</v>
+        <v>2434.58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5183,7 +5211,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5253,7 +5281,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>675</v>
+        <v>1025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5281,7 +5309,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5351,7 +5379,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2213.65</v>
+        <v>3008.65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5362,7 +5390,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>paul welch</t>
+          <t>adrienne paul</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5375,11 +5403,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>850</v>
+        <v>1412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5390,7 +5418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>adrienne paul</t>
+          <t>paul welch</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5403,11 +5431,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>612</v>
+        <v>860</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5477,7 +5505,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2821.89</v>
+        <v>4389.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5505,7 +5533,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>945</v>
+        <v>990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5575,7 +5603,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6783.7</v>
+        <v>16204.77</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5673,7 +5701,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5701,7 +5729,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5771,7 +5799,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3091.7</v>
+        <v>6155.59</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5799,7 +5827,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1110</v>
+        <v>1250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5869,7 +5897,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12760</v>
+        <v>18411.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5950,7 +5978,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nicole richards</t>
+          <t>arthur k mingo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5963,11 +5991,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2705.29</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5978,7 +6006,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>arthur k mingo</t>
+          <t>nicole richards</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5991,7 +6019,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -6065,7 +6093,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>73158.3</v>
+        <v>143087.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6093,7 +6121,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6121,7 +6149,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>305</v>
+        <v>325.04</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6191,7 +6219,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1201.53</v>
+        <v>8155.22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6272,7 +6300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scott girardin</t>
+          <t>stephen j wood</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6285,11 +6313,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6300,7 +6328,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stephen j wood</t>
+          <t>scott girardin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6313,7 +6341,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
@@ -6332,7 +6360,7 @@
 
 <file path=xl/worksheets/sheet146.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6370,7 +6398,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>julia a g mccabe</t>
+          <t>chad syphers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6383,11 +6411,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1170</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6398,7 +6426,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chad syphers</t>
+          <t>julia a g mccabe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6411,13 +6439,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>970</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_93</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>susan g longchamps</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>93</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Republican</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_93</t>
         </is>
@@ -6468,7 +6524,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>janet beaudoin</t>
+          <t>scott a harriman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6481,11 +6537,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>3850</v>
+        <v>33390.33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6496,7 +6552,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scott a harriman</t>
+          <t>janet beaudoin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6509,11 +6565,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>11203.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6583,7 +6639,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8201</v>
+        <v>56622.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6594,7 +6650,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matthew kershaw</t>
+          <t>bret michael martel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6607,11 +6663,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>927.53</v>
+        <v>2551.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6622,7 +6678,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bret michael martel</t>
+          <t>matthew kershaw</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6635,11 +6691,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1768.82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6692,7 +6748,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kerryl lee clement</t>
+          <t>luke jensen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6705,11 +6761,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1085</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6720,7 +6776,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>luke jensen</t>
+          <t>kerryl lee clement</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6733,11 +6789,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6807,7 +6863,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1600</v>
+        <v>2550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7059,7 +7115,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7255,7 +7311,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1634</v>
+        <v>1634.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7270,7 +7326,7 @@
 
 <file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7356,6 +7412,34 @@
         <v>551</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>jaric t fontaine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_10</t>
         </is>
@@ -7406,7 +7490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>glenn chip curry</t>
+          <t>ryan christopher otis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7419,11 +7503,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>3045</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7434,7 +7518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ryan christopher otis</t>
+          <t>glenn chip curry</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7447,11 +7531,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>3000</v>
+        <v>2940</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7521,7 +7605,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7745,7 +7829,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5000</v>
+        <v>17727.06</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7773,7 +7857,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>4733.34</v>
+        <v>13069.13</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7843,7 +7927,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3105</v>
+        <v>3075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7871,7 +7955,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1300</v>
+        <v>1490</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8039,7 +8123,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8109,7 +8193,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2225.5</v>
+        <v>3858.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8120,7 +8204,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jojean keller</t>
+          <t>joshua morris</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8133,11 +8217,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1350</v>
+        <v>3089.39</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8148,7 +8232,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>joshua morris</t>
+          <t>jojean keller</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8161,11 +8245,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8235,7 +8319,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9604.48</v>
+        <v>12217.32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8263,7 +8347,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2965</v>
+        <v>2865</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8333,7 +8417,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4100</v>
+        <v>7299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8344,7 +8428,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peter j southam</t>
+          <t>david duguay</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8357,11 +8441,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>2835</v>
+        <v>5100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8372,7 +8456,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>david duguay</t>
+          <t>peter j southam</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8385,11 +8469,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2835</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8404,7 +8488,7 @@
 
 <file path=xl/worksheets/sheet164.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8442,7 +8526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>harold hull</t>
+          <t>harold trey l iii stewart</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8455,11 +8539,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>2495</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8470,7 +8554,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>harold trey l iii stewart</t>
+          <t>harold hull</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8483,13 +8567,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>janel c underwoodcharette</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_2</t>
         </is>
@@ -8557,7 +8669,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2935</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8585,7 +8697,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2885</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8655,7 +8767,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>19730</v>
+        <v>29319.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8683,7 +8795,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2463</v>
+        <v>3000.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8781,7 +8893,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2994.2</v>
+        <v>3029.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8879,7 +8991,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>2723.1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8907,7 +9019,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>700</v>
+        <v>2395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8977,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5775</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9145,7 +9257,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3400</v>
+        <v>3650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9215,7 +9327,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12000</v>
+        <v>40100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9271,7 +9383,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>2975</v>
+        <v>2885</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9341,7 +9453,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1400</v>
+        <v>1840</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9411,7 +9523,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1618.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9481,7 +9593,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>17000</v>
+        <v>24200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9509,7 +9621,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>10405</v>
+        <v>10593.17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9524,7 +9636,7 @@
 
 <file path=xl/worksheets/sheet175.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9579,7 +9691,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12406.51</v>
+        <v>17863.07</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9607,7 +9719,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3000</v>
+        <v>6760.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9618,7 +9730,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stanley short jr</t>
+          <t>ester franklin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9635,9 +9747,37 @@
         </is>
       </c>
       <c r="E4">
+        <v>170</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Senator_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>stanley short jr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Senator_3</t>
         </is>
@@ -9650,7 +9790,7 @@
 
 <file path=xl/worksheets/sheet176.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9705,7 +9845,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3425</v>
+        <v>3005</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9744,7 +9884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>harry white</t>
+          <t>m thad moody</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9764,6 +9904,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Senator_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>harry white</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Senator_30</t>
         </is>
@@ -9776,7 +9944,7 @@
 
 <file path=xl/worksheets/sheet177.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9842,7 +10010,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>garrett plummer</t>
+          <t>scott benedetto eccleston</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9862,6 +10030,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Senator_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>garrett plummer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senator</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>31</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Senator_31</t>
         </is>
@@ -9912,7 +10108,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>henry l ingwersen</t>
+          <t>jason g litalien</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9925,11 +10121,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E2">
-        <v>2400</v>
+        <v>5910.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9940,7 +10136,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jason g litalien</t>
+          <t>henry l ingwersen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9953,11 +10149,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>1100</v>
+        <v>2950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10027,7 +10223,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6425</v>
+        <v>22430.52</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10055,7 +10251,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3015</v>
+        <v>2960</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10251,7 +10447,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3044</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10349,7 +10545,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3101</v>
+        <v>3186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10430,7 +10626,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>joseph paul guerin</t>
+          <t>chad richard perkins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10447,7 +10643,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6120</v>
+        <v>8524.84</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10458,7 +10654,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chad richard perkins</t>
+          <t>joseph paul guerin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10475,7 +10671,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>5974.7</v>
+        <v>6225</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10503,7 +10699,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>2250</v>
+        <v>4050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10531,7 +10727,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1540</v>
+        <v>1657</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -10559,7 +10755,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20.18</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -10657,7 +10853,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10727,7 +10923,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16440</v>
+        <v>25620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10783,7 +10979,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -10881,7 +11077,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10934,7 +11130,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leo christopher kenney</t>
+          <t>michael tipping</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10947,11 +11143,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>2980</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10962,7 +11158,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>michael tipping</t>
+          <t>leo christopher kenney</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10975,11 +11171,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>2400</v>
+        <v>2980</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11049,7 +11245,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11147,7 +11343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1041</v>
+        <v>1146</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11162,7 +11358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11217,7 +11413,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>26685.78</v>
+        <v>28352.13</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11228,7 +11424,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dana marie appleby</t>
+          <t>jennifer l levesque</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11248,6 +11444,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dana marie appleby</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_1</t>
         </is>
@@ -11315,7 +11539,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3715</v>
+        <v>3940</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11455,7 +11679,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>750</v>
+        <v>3645</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11623,7 +11847,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11693,7 +11917,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11791,7 +12015,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>39041</v>
+        <v>39562.31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11834,7 +12058,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11900,7 +12124,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>meagan smith</t>
+          <t>lucy louisa perkins</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11913,13 +12137,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_121</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>meagan smith</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>121</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_121</t>
         </is>
@@ -11987,7 +12239,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>3968.42</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12155,7 +12407,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>4865.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12166,7 +12418,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>william r tuell</t>
+          <t>genevieve lemire</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12179,11 +12431,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>400</v>
+        <v>690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12194,7 +12446,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>genevieve lemire</t>
+          <t>william r tuell</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12207,11 +12459,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -12309,7 +12561,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>985</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12477,7 +12729,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4325</v>
+        <v>6441.46</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12505,7 +12757,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2100</v>
+        <v>3226.31</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12743,7 +12995,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>360</v>
+        <v>5761.24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12911,7 +13163,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>977.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12939,7 +13191,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13107,7 +13359,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>140</v>
+        <v>1334.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13177,7 +13429,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13275,7 +13527,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4835</v>
+        <v>11166.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13373,7 +13625,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3600</v>
+        <v>3676</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13471,7 +13723,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13499,7 +13751,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>947</v>
+        <v>947.02</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13597,7 +13849,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2850</v>
+        <v>6700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13695,7 +13947,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2775</v>
+        <v>11258.71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13723,7 +13975,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>945</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13793,7 +14045,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13821,7 +14073,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1045</v>
+        <v>1095</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13891,7 +14143,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2555</v>
+        <v>2975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14087,7 +14339,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6775</v>
+        <v>21819.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14115,7 +14367,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14185,7 +14437,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2472.72</v>
+        <v>7084.73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14213,7 +14465,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>1000.98</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14269,7 +14521,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>775</v>
+        <v>1000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -14367,7 +14619,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14382,7 +14634,7 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14448,7 +14700,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gordon frohloff</t>
+          <t>domingo e torres</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14468,6 +14720,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_142</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gordon frohloff</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_142</t>
         </is>
@@ -14480,7 +14760,7 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14535,7 +14815,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>3000.04</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14566,6 +14846,34 @@
         <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_143</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>melissa a simpson</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>143</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_143</t>
         </is>
@@ -14578,7 +14886,7 @@
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14616,7 +14924,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corinna cole</t>
+          <t>jeff adams</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14629,11 +14937,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>371.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14644,7 +14952,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jeff adams</t>
+          <t>corinna cole</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14657,13 +14965,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_144</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>karen a gerrish</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Republican</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_144</t>
         </is>
@@ -14759,7 +15095,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950</v>
+        <v>995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14942,7 +15278,7 @@
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14997,7 +15333,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>3509.36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15036,7 +15372,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noah cobb</t>
+          <t>marissa l tasker</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -15049,13 +15385,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>Representative_148</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>noah cobb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unenrolled</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Representative_148</t>
         </is>
@@ -15123,7 +15487,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1100</v>
+        <v>3400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15330,7 +15694,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mark frederick zimmer</t>
+          <t>alexandros orestis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -15343,11 +15707,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>920</v>
+        <v>1075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15358,7 +15722,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alexandros orestis</t>
+          <t>mark frederick zimmer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -15371,11 +15735,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>875</v>
+        <v>920</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -15445,7 +15809,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1450</v>
+        <v>3229.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15543,7 +15907,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15767,7 +16131,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>13010</v>
+        <v>15929.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15963,7 +16327,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8232.709999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15991,7 +16355,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16061,7 +16425,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16187,7 +16551,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16313,7 +16677,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>138.22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16383,7 +16747,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>750</v>
+        <v>1299.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16565,7 +16929,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16635,7 +16999,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>975</v>
+        <v>1175</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16705,7 +17069,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16999,7 +17363,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>850</v>
+        <v>5301.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17027,7 +17391,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>310</v>
+        <v>385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17097,7 +17461,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1290</v>
+        <v>1290.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17195,7 +17559,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>985</v>
+        <v>1035</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17223,7 +17587,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17251,7 +17615,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>525</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -17262,7 +17626,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nancy theriaultspecial</t>
+          <t>james michael michaud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17279,7 +17643,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>964.33</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -17290,7 +17654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>james michael michaud</t>
+          <t>nancy theriaultspecial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17377,7 +17741,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4550</v>
+        <v>6100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17405,7 +17769,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17433,7 +17797,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>313.39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -17503,7 +17867,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>600</v>
+        <v>2784.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17584,7 +17948,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eric boothroyd</t>
+          <t>andrew r torbett</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17597,11 +17961,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>625</v>
+        <v>3565</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17612,7 +17976,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>andrew r torbett</t>
+          <t>eric boothroyd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17625,11 +17989,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>1125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17699,7 +18063,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>2950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17769,7 +18133,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>11526.76</v>
+        <v>12731.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17797,7 +18161,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17867,7 +18231,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2100</v>
+        <v>2600.66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17895,7 +18259,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>42.54</v>
+        <v>168.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17965,7 +18329,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3630.65</v>
+        <v>18002.47</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18046,7 +18410,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>james e thorne</t>
+          <t>debora farnham</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18059,11 +18423,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>505</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18074,7 +18438,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>debora farnham</t>
+          <t>james e thorne</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18087,11 +18451,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18259,7 +18623,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>15275</v>
+        <v>33840.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18287,7 +18651,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18340,7 +18704,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kayla miller</t>
+          <t>benjamin charles hymes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18353,11 +18717,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>900</v>
+        <v>2437.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18385,7 +18749,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>310</v>
+        <v>1210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18396,7 +18760,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benjamin charles hymes</t>
+          <t>kayla miller</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18409,11 +18773,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -18483,7 +18847,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2850</v>
+        <v>3850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18651,7 +19015,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1150</v>
+        <v>1210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18749,7 +19113,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1070</v>
+        <v>3070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -18973,7 +19337,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>555</v>
+        <v>1673.46</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19054,7 +19418,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>chris p austin</t>
+          <t>rhiannon hampson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19067,11 +19431,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>4779.74</v>
+        <v>9604.469999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19082,7 +19446,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rhiannon hampson</t>
+          <t>chris p austin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19095,11 +19459,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>2870</v>
+        <v>5335.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19225,7 +19589,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8319.799999999999</v>
+        <v>8369.799999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19236,7 +19600,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shawn saindon</t>
+          <t>brady alden clark</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19249,11 +19613,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E3">
-        <v>1013.84</v>
+        <v>2006.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19264,7 +19628,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brady alden clark</t>
+          <t>shawn saindon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19277,11 +19641,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1063.84</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19351,7 +19715,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>18040</v>
+        <v>24962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19379,7 +19743,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3756.18</v>
+        <v>5530.13</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19575,7 +19939,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19726,7 +20090,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nicolas john hamlin</t>
+          <t>trent vellella</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19739,11 +20103,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19754,7 +20118,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>suzanne r andresen</t>
+          <t>nicolas john hamlin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19782,7 +20146,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trent vellella</t>
+          <t>suzanne r andresen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19795,11 +20159,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E4">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19814,7 +20178,7 @@
 
 <file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -19880,7 +20244,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bruce archer</t>
+          <t>lori g kenneson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19900,6 +20264,34 @@
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Representative_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bruce archer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Representative</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Democratic</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Representative_5</t>
         </is>
@@ -19950,7 +20342,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>david a sinclair</t>
+          <t>jedediah j rice</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19963,11 +20355,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19978,7 +20370,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jedediah j rice</t>
+          <t>david a sinclair</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19991,7 +20383,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6198.57</v>
+        <v>6248.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5761.24</v>
+        <v>5786.24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/viz/data/clean/maine_races_by_district.xlsx
+++ b/viz/data/clean/maine_races_by_district.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3041723.78</v>
+        <v>3039523.78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1914913.56</v>
+        <v>1910163.56</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>1478574.28</v>
+        <v>1476415.96</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>1335066.66</v>
+        <v>1334066.66</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>1136899</v>
+        <v>1133469</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>781022.95</v>
+        <v>781017.95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>553696.87</v>
+        <v>551996.87</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>541291.22</v>
+        <v>539837.01</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>17389.7</v>
+        <v>17025</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1660</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8222.5</v>
+        <v>7892.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1370</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1145</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>21.15</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>14367.43</v>
+        <v>12967.43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1001</v>
+        <v>951</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2410.03</v>
+        <v>2210.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2070</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>8141.7</v>
+        <v>8116.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>919.47</v>
+        <v>819.47</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5475</v>
+        <v>4975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2434.58</v>
+        <v>2254.58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1412</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4389.7</v>
+        <v>3464.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>16204.77</v>
+        <v>15721.07</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>143087.25</v>
+        <v>142847.25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scott a harriman</t>
+          <t>janet beaudoin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6537,11 +6537,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>33390.33</v>
+        <v>11203.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>janet beaudoin</t>
+          <t>scott a harriman</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6565,11 +6565,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>11203.6</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1768.82</v>
+        <v>1718.82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>luke jensen</t>
+          <t>kerryl lee clement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6761,11 +6761,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1085</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kerryl lee clement</t>
+          <t>luke jensen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2555</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ann higgins matlack</t>
+          <t>roy gott</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7629,11 +7629,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Unenrolled</t>
         </is>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>roy gott</t>
+          <t>ann higgins matlack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unenrolled</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3075</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2906</v>
+        <v>2736</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1416</v>
+        <v>1316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>29319.01</v>
+        <v>28964.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3029.2</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>4075</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3650</v>
+        <v>3450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>24200</v>
+        <v>23200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>10593.17</v>
+        <v>193.17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3005</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>2960</v>
+        <v>2795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3055</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>6248.57</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>3186</v>
+        <v>2885</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1340</v>
+        <v>905</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1146</v>
+        <v>871</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>28352.13</v>
+        <v>28102.13</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3940</v>
+        <v>3765</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3645</v>
+        <v>2895</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1532</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>39562.31</v>
+        <v>38677.31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>3968.42</v>
+        <v>3868.42</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>690</v>
+        <v>515</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1060</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5786.24</v>
+        <v>5411.24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1275</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1095</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>poppy t arford</t>
+          <t>ravi jackson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14587,11 +14587,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>658.3199999999999</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ravi jackson</t>
+          <t>poppy t arford</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14615,11 +14615,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1160</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1075</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1115.54</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>joschka winterling</t>
+          <t>victoria porter kornfield</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>792.27</v>
+        <v>725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>victoria porter kornfield</t>
+          <t>joschka winterling</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>725</v>
+        <v>452.27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1175</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>2555</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1290.01</v>
+        <v>1000.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nancy mcdowell</t>
+          <t>nancy jean theriault</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17555,11 +17555,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nancy mcdowellspecial</t>
+          <t>nancy mcdowell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nancy jean theriault</t>
+          <t>james michael michaud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17615,7 +17615,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>964.33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>james michael michaud</t>
+          <t>nancy mcdowellspecial</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17639,11 +17639,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E5">
-        <v>964.33</v>
+        <v>950</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1125</v>
+        <v>600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jason cherry</t>
+          <t>kayla miller</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1210</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kayla miller</t>
+          <t>jason cherry</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19124,7 +19124,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>marcus mrowka</t>
+          <t>joshua d gerritsen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19141,7 +19141,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1070</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>joshua d gerritsen</t>
+          <t>marcus mrowka</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19169,7 +19169,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>9604.469999999999</v>
+        <v>9334.469999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>1063.84</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>24962</v>
+        <v>24487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trent vellella</t>
+          <t>nicolas john hamlin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20103,11 +20103,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="E2">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nicolas john hamlin</t>
+          <t>suzanne r andresen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20146,7 +20146,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>suzanne r andresen</t>
+          <t>trent vellella</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Republican</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="E4">
